--- a/Медосмотры_сверка_штатка_05.10.2026.xlsx
+++ b/Медосмотры_сверка_штатка_05.10.2026.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2340" uniqueCount="926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2357" uniqueCount="944">
   <si>
     <t xml:space="preserve">Учёт предварительных и периодических медицинских осмотров</t>
   </si>
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Слабые места и допущения, требующие внимания:</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Периодичность периодического осмотра (12 месяцев) проверена построчно по таблице "Периодичность и объём..." из приложения к Порядку (Приказ №29н от 28.01.2021): для каждой из 45 должностей взят минимальный интервал среди её пунктов, так как проводится один совмещённый осмотр и он не может быть реже наиболее частого фактора (пункт 18 Порядка). Для всех 45 должностей хотя бы один пункт требует ежегодного осмотра, поэтому 12 месяцев подтверждено для каждой строки, - обоснование указано в столбце «Обоснование периодичности» на листе «Перечень должностей». Отдельно учитывайте правило: работники моложе 21 года проходят периодические осмотры ежегодно вне зависимости от фактора (пункт 18 Порядка).</t>
+    <t xml:space="preserve">1. Периодичность (12 мес.) ПРОВЕРЕНА 13.10.2026 по тексту Приказа №29н (КонсультантПлюс, ред. 327н от 29.04.2026): для всех 45 позиций минимальный интервал — 1 раз в год, столбец «Обоснование периодичности» совпадает с таблицей приложения. Работники моложе 21 года — ежегодно (п.18 Порядка).</t>
   </si>
   <si>
     <t xml:space="preserve">2. Для части должностей («Инженер», «Ведущий инженер», «Контролер») исходный файл не уточнял, к какому пункту Перечня они относятся: соответствие определено формулой по названию подразделения (ОТК или ПДО). При переименовании подразделений формулу на листе «Учёт медосмотров» (столбец G) нужно будет пересмотреть.</t>
@@ -100,7 +100,7 @@
     <t xml:space="preserve">5. Ни для одного сотрудника ещё не зафиксирована дата фактически пройденного периодического осмотра, поэтому все расчётные даты очередного осмотра - это первый плановый цикл от даты предварительного осмотра. По мере прохождения периодических осмотров вносите их даты в столбец «Факт. дата последнего пройденного периодического осмотра», и следующая дата пересчитается автоматически.</t>
   </si>
   <si>
-    <t xml:space="preserve">6. Список должностей, подлежащих психиатрическому освидетельствованию по Приказу №342н, определён по названию должности и общей логике вида деятельности (управление транспортом - п.1 Приложения №2; работа с электроустановками - п.11-12), это помечено «Да». Для должностей Главный механик, Сборщик стеклопластиковых изделий, Старший сторож/сторож/старший оперативный дежурный/оперативный дежурный совпадение с категориями Приложения №2 первоначально выглядело вероятным (сосуды под давлением/автоклавы, оружие у охраны), но специалист по охране труда подтвердил, что эти должности освидетельствование не проходят, - в столбце «Психиатрическое освидетельствование» проставлено «Нет» с примечанием об этом уточнении. ИСПРАВЛЕНО 13.10.2026: по Приказу №342н (с 01.09.2022) периодичность освидетельствования не установлена (письмо Минздрава №30-0/3066769); дата «+5 лет» в столбце P — только внутренняя контрольная мера, не требование закона («5 лет» в ст.6 Закона №3185-1 — срок временной непригодности, а не периодичность). С 01.03.2026 действуют изменения 342н (Приказ №392н от 02.07.2025) — нумерацию пунктов Приложения №2 сверить.</t>
+    <t xml:space="preserve">6. Список должностей, подлежащих психиатрическому освидетельствованию по Приказу №342н, определён по названию должности и общей логике вида деятельности (управление транспортом - п.1 Приложения №2; работа с электроустановками - п.11-12), это помечено «Да». Для должностей Главный механик, Сборщик стеклопластиковых изделий, Старший сторож/сторож/старший оперативный дежурный/оперативный дежурный совпадение с категориями Приложения №2 первоначально выглядело вероятным (сосуды под давлением/автоклавы, оружие у охраны), но специалист по охране труда подтвердил, что эти должности освидетельствование не проходят, - в столбце «Психиатрическое освидетельствование» проставлено «Нет» с примечанием об этом уточнении. ИСПРАВЛЕНО 13.10.2026: по Приказу №342н (с 01.09.2022) периодичность освидетельствования не установлена (письмо Минздрава №30-0/3066769); дата «+5 лет» в столбце P — только внутренняя контрольная мера, не требование закона («5 лет» в ст.6 Закона №3185-1 — срок временной непригодности, а не периодичность). С 01.03.2026 действуют изменения 342н (Приказ №392н от 02.07.2025) — нумерацию пунктов Приложения №2 сверить. УТОЧНЕНО 13.10.2026 по тексту 342н: п.11 Приложения №2 относится к сфере электроэнергетики (35-ФЗ) — для электромонтажников и мастеров электромонтажных участков (п.20, п.29 Перечня) статус изменён на «Проверить».</t>
   </si>
   <si>
     <t xml:space="preserve">7. ИСПРАВЛЕНО 10.09.2026: список сотрудников пересобран заново напрямую из штатного расписания (736 сотрудников на 04.09.2026), а не из ранее использовавшегося отдельного файла учёта - тот файл оказался неполным и не отражал новых сотрудников (например, Раззакову Светлану Владимировну, уборщика производственных и служебных помещений, принятую 27.08.2026, - обнаружено пользователем при ручной проверке). При пересборке также учтено, что должности в штатном расписании содержат разряд/категорию (например, «Столяр 5 разряда», «Инженер 2 категории») - формула сопоставления на листе «Учёт медосмотров» (столбец G) теперь отбрасывает эти суффиксы при поиске пункта Перечня. В результате: добавлено 21 новых сотрудника (включая Раззакову С.В.), исключено 10 - из них 6 больше не значатся в штатном расписании (уволены), а 4 (Добролюбова Г.М., Кляцкин А.Б., Лазебников В.В., Пушкин С.О.) переведены на должности вне перечня Приказа №43. Итоговая численность выросла с 352 до 363 человек. Также обнаружено: по должности «Инженер по эксплуатации» (№17 Перечня) сейчас нет ни одного сотрудника в штате - это не ошибка, а фактическое отсутствие занятых ставок. Рекомендуется впредь сверять этот файл со штатным расписанием при каждом обновлении последнего, так как найденный пробел показывает, что расхождения возникают быстро.</t>
@@ -712,10 +712,10 @@
     <t xml:space="preserve">Периодичность периодического осмотра 12 мес.</t>
   </si>
   <si>
-    <t xml:space="preserve">Для совмещённого осмотра берётся наименьший интервал среди пунктов. Проверено по источникам: п.4.4 «Шум» — 1 раз в год (есть в 44 из 45 позиций → 12 мес. обоснованы); п.4.6 «Инфразвук» — 1 раз в год; п.4.2 (в т.ч. 4.2.1 лазерное) и п.4.3.1 (локальная вибрация) — 1 раз в 2 года. Исключение — позиция №45 (сторожа, оперативные дежурные: п.4.7, 4.8, 5.1, 5.2): п.4.4 нет, ежегодность опирается на п.5.1 — не подтверждено. 12 мес. в любом случае допустимы (чаще нормы — не нарушение).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Соответствует; по №45 сверить с таблицей 29н</t>
+    <t xml:space="preserve">Сверено по тексту 29н (ред. 327н от 29.04.2026), приложение к Порядку. Все 45 позиций: минимальный интервал 1 раз в год, столбец «Обоснование» совпадает полностью. №45 (сторожа) — ежегодно по п.5.1 «Тяжесть трудового процесса» (1 раз в год).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Соответствует (подтверждено по первоисточнику)</t>
   </si>
   <si>
     <t xml:space="preserve">7.6</t>
@@ -733,7 +733,7 @@
     <t xml:space="preserve">Психиатрическое освидетельствование, «1 раз в 5 лет»</t>
   </si>
   <si>
-    <t xml:space="preserve">ОШИБКА в прежней версии. Приказ №342н (с 01.09.2022) кратность не устанавливает (письмо Минздрава №30-0/3066769). Освидетельствование — при приёме на вид деятельности из Прил. №2 и по направлению по итогам медосмотра. Столбец P и строка дашборда переименованы во «внутреннюю контрольную дату». «5 лет» в ч.1 ст.6 Закона №3185-1 (ред. 465-ФЗ) — максимальный срок временной непригодности, а не периодичность; сноска на листе «Перечень» исправлена.</t>
+    <t xml:space="preserve">Текст 342н (ред. 392н): периодичности нет. Освидетельствование — при приёме на вид деятельности из Прил.№2 (п.1), по признакам психического расстройства по итогам периодического осмотра (п.4(1)). Повторно не требуется, если работник ранее (не позднее 2 лет) проходил его по тому же виду деятельности и признан пригодным (п.5). «Не более пяти лет» (п.4(2), ст.6 Закона №3185-1) — срок временной непригодности. Столбец P — внутренняя мера.</t>
   </si>
   <si>
     <t xml:space="preserve">Исправлено</t>
@@ -745,10 +745,10 @@
     <t xml:space="preserve">Изменения 342н с 01.03.2026 (Приказ №392н от 02.07.2025)</t>
   </si>
   <si>
-    <t xml:space="preserve">Изменены Приложения №1 и №2 (комиссия врачей-психиатров; исключена гостайна). Номера пунктов Прил. №2 («п.1», «п.11–12») на листе «Перечень» указаны по старой редакции.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сверить нумерацию с действующей редакцией</t>
+    <t xml:space="preserve">Текст 342н в ред. 392н: нумерация Приложения №2 сохранена (п.10 утратил силу с 01.03.2026). п.1 — транспорт (ПП №2349), п.11 — электроэнергетика, п.12 — теплоснабжение, п.13 — оборудование под давлением, учтённое в Ростехнадзоре, п.6 — краны, учтённые в Ростехнадзоре, п.4 — оборот оружия.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ссылки на листе «Перечень» корректны</t>
   </si>
   <si>
     <t xml:space="preserve">7.9</t>
@@ -802,10 +802,10 @@
     <t xml:space="preserve">Психиатрическое освидетельствование у бывших монтажников ЭО ЛА</t>
   </si>
   <si>
-    <t xml:space="preserve">Богданов А.В., Озорнов И.В., Романов Д.Е., Шабалин А.С. стали электромонтажниками (п.20: «Да» — работы в электроустановках). По п.37 освидетельствование не требовалось. Дат освидетельствования в учёте нет.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Направить на освидетельствование до допуска к работам в электроустановках</t>
+    <t xml:space="preserve">По тексту 342н п.11 Прил.№2 касается «сферы электроэнергетики» (35-ФЗ). Электромонтажники участков РЭО (32 чел., п.20) и мастера (2 чел., п.29) монтируют бортовое ЭО изделий — по буквальному прочтению это не электроэнергетика. На листе «Перечень» для №20 и №29 статус изменён с «Да» на «Проверить». Сюда относятся и Богданов, Озорнов, Романов, Шабалин (бывшие монтажники ЭО ЛА).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Решение работодателя с фиксацией основания</t>
   </si>
   <si>
     <t xml:space="preserve">7.14</t>
@@ -856,6 +856,54 @@
     <t xml:space="preserve">Рекомендуется добавить в учёт столбец СНИЛС</t>
   </si>
   <si>
+    <t xml:space="preserve">7.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Наименования в списке контингента (п.21 Порядка 29н)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«В списке работников... указывается наименование профессии (должности) работника согласно штатному расписанию». Приказ №43 использует «Столяр», «Маляр», «Оператор станка с ЧПУ», а в штатке теперь «Техник-сборщик», «Техник», «Оператор станков с ЧПУ».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прямое основание изменить Приказ №43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Поимённые списки (п.23–24 Порядка 29н)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В поимённом списке обязательны ФИО, должность, СТАЖ РАБОТЫ В НЕЙ, подразделение, факторы. Стажа в учёте нет (есть только дата приёма). Список направляется в медорганизацию не позднее чем за 2 месяца до начала осмотра.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Добавить стаж при формировании поимённого списка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Центр профпатологии (п.40 Порядка 29н)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">При стаже 5 лет во вредных условиях (подклассы 3.1–3.4) первый периодический осмотр — в центре профпатологии, далее раз в 5 лет. В учёте 88 человек приняты 5 и более лет назад (Машково 61, Воронеж 9, Внуково 6, Руднево 6, Москва 5, Казань 1). Классы условий труда в файле не отражены.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сопоставить с картами СОУТ; при классе 3.1+ — включить в график профпатологии</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Условия по 342н для «Нет» / «-»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Главный механик, сборщик стеклопластиковых изделий — «Да», если непосредственно обслуживают оборудование под давлением &gt;0,07 МПа, учтённое в Ростехнадзоре (п.13). Кладовщики — если управляют кранами, учтёнными в Ростехнадзоре (п.6). Сторожа — если работают с оружием (п.4).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подтвердить по фактическим работам</t>
+  </si>
+  <si>
     <t xml:space="preserve">№ п/п</t>
   </si>
   <si>
@@ -904,7 +952,7 @@
     <t xml:space="preserve">Да</t>
   </si>
   <si>
-    <t xml:space="preserve">п.11 Приложения №2 (монтаж, наладка, техобслуживание, ремонт, управление режимом работы электроустановок)</t>
+    <t xml:space="preserve">п.11 Приложения №2 (сфера электроэнергетики: монтаж, наладка, техобслуживание, ремонт, управление режимом работы электроустановок). Применимо при обслуживании электроустановок предприятия (электротехнический персонал)</t>
   </si>
   <si>
     <t xml:space="preserve">Механик</t>
@@ -937,7 +985,7 @@
     <t xml:space="preserve">Нет</t>
   </si>
   <si>
-    <t xml:space="preserve">уточнено специалистом по охране труда: главный механик психиатрическое освидетельствование не проходит</t>
+    <t xml:space="preserve">уточнено специалистом по охране труда: главный механик психиатрическое освидетельствование не проходит. Условие: при непосредственном обслуживании оборудования под давлением &gt;0,07 МПа, учтённого в Ростехнадзоре, — п.13 Прил.№2, тогда «Да»</t>
   </si>
   <si>
     <t xml:space="preserve">Разнорабочий</t>
@@ -985,6 +1033,9 @@
     <t xml:space="preserve">Старший кладовщик, кладовщик, кладовщик-комплектовщик</t>
   </si>
   <si>
+    <t xml:space="preserve">Условие: при управлении кранами, учтёнными в Ростехнадзоре, — п.6 Прил.№2, тогда «Да»</t>
+  </si>
+  <si>
     <t xml:space="preserve">Лаборант</t>
   </si>
   <si>
@@ -1018,7 +1069,10 @@
     <t xml:space="preserve">п.4.3.1, п.4.3.2, п.4.4, п.4.9, п.5.1, п.5.2, п.6.2, п.9</t>
   </si>
   <si>
-    <t xml:space="preserve">п.11 Приложения №2 (электроустановки)</t>
+    <t xml:space="preserve">Проверить</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРОВЕРИТЬ (13.10.2026, по тексту 342н в ред. 392н): п.11 Приложения №2 — «деятельность в сфере ЭЛЕКТРОЭНЕРГЕТИКИ» (ст.3 Федерального закона №35-ФЗ) — монтаж, наладка, техобслуживание, ремонт, управление режимом электроустановок. Монтаж бортового электрооборудования/жгутов изделий (участки РЭО) к электроэнергетике, по буквальному прочтению, не относится. Решение — за работодателем: при подтверждении работ в электроустановках предприятия — «Да», иначе — «Нет»; основание зафиксировать.</t>
   </si>
   <si>
     <t xml:space="preserve">Столяр</t>
@@ -1051,7 +1105,7 @@
     <t xml:space="preserve">п.1.37.1, п.4.4, п.5.1</t>
   </si>
   <si>
-    <t xml:space="preserve">уточнено специалистом по охране труда: сборщик стеклопластиковых изделий психиатрическое освидетельствование не проходит</t>
+    <t xml:space="preserve">уточнено специалистом по охране труда: сборщик стеклопластиковых изделий психиатрическое освидетельствование не проходит. Условие: если сборщик непосредственно обслуживает автоклав (&gt;0,07 МПа), учтённый в Ростехнадзоре, — п.13 Прил.№2, тогда «Да»</t>
   </si>
   <si>
     <t xml:space="preserve">Ведущий специалист по учёту ПДО, ведущий инженер ПДО, инженер ПДО</t>
@@ -1153,7 +1207,7 @@
     <t xml:space="preserve">уточнено специалистом по охране труда: сторожа и оперативные дежурные психиатрическое освидетельствование не проходят</t>
   </si>
   <si>
-    <t xml:space="preserve">Периодичность проверена построчно по таблице "Периодичность и объём обязательных предварительных и периодических медицинских осмотров работников" (приложение к Порядку, утв. Приказом Минздрава №29н от 28.01.2021). Для позиции с несколькими вредными факторами применяется наименьший (наиболее частый) из указанных интервалов, так как проводится один совмещённый осмотр (пункт 18 Порядка: осмотры проводятся "не реже чем в сроки", предусмотренные приложением). По всем 45 должностям хотя бы один фактор требует ежегодного осмотра, поэтому итоговая периодичность для всех позиций составляет 12 месяцев. Столбец «Обоснование периодичности» показывает, какой именно пункт(ы) это определяют. Жёлтым выделено редактируемое поле: скорректируйте его, если после специальной оценки условий труда состав факторов по должности изменится, а также учитывайте отдельное правило пункта 18 Порядка: работники моложе 21 года проходят периодические осмотры ежегодно независимо от фактора.</t>
+    <t xml:space="preserve">ПРОВЕРЕНО 13.10.2026 по тексту Приказа Минздрава №29н (КонсультантПлюс, ред. 44н, 509н, 327н от 29.04.2026), приложение к Порядку: для всех 45 позиций минимальный интервал = 1 раз в год; столбец «Обоснование» совпадает с таблицей полностью. Ежегодные пункты: 4.4 «Шум», 4.6 «Инфразвук», 5.1 «Тяжесть трудового процесса», 6 «Работы на высоте» (в т.ч. 6.1, 6.2), 1.8.4, 1.12, 1.14.2, 1.15, 1.27, 1.36, 1.37.1, 1.44, 1.45.x. Раз в 2 года: 1.25, 1.48, 1.49.x, 1.50, 3.1.8.3, 4.2.x, 4.3.x, 4.7, 4.8, 4.9, 5.2, 9, 15, 17, 18.1. Правило п.18 Порядка: осмотры не реже сроков приложения; работники до 21 года — ежегодно. Замечание к Приказу №43: позиция №38 указывает «п.18» без подпункта — периодичность задана только для подпунктов (18.1 — кат. A, B, BE; 18.2 — C, C1, CE, D1, D1E); нужно указать подпункт по категории ТС.</t>
   </si>
   <si>
     <t xml:space="preserve">Столбец «Психиатрическое освидетельствование (Приказ №342н)» заполнен по Приложению №2 к Приказу Минздрава №342н от 20.05.2022 (виды деятельности, при которых проводится обязательное психиатрическое освидетельствование). «Да» — должность соответствует виду деятельности (управление транспортными средствами; работы в электроустановках). Главный механик, Сборщик стеклопластиковых изделий, сторожа/оперативные дежурные — «Нет» по уточнению специалиста по охране труда (08.09.2026). ИСПРАВЛЕНО 13.10.2026: периодичность освидетельствования действующим законодательством НЕ установлена — Приказ №342н кратность не определяет (письмо Минздрава №30-0/3066769); «пять лет» в ч.1 ст.6 Закона РФ №3185-1 (ред. 465-ФЗ от 04.08.2023) — это максимальный срок признания работника временно непригодным, а не интервал освидетельствований. Освидетельствование проводится при приёме (переводе) на вид деятельности из Приложения №2 и по направлению по итогам медосмотра. С 01.03.2026 действуют изменения Приложений №1 и №2 (Приказ №392н от 02.07.2025) — номера пунктов Приложения №2 сверить с действующей редакцией.</t>
@@ -3069,7 +3123,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="20">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3160,7 +3214,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFDDEBF7"/>
+          <fgColor rgb="FFFCE4D6"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -3168,7 +3222,15 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFCE4D6"/>
+          <fgColor rgb="FF974706"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDDEBF7"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -3685,7 +3747,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
@@ -5251,7 +5313,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="9" t="s">
         <v>255</v>
       </c>
@@ -5265,7 +5327,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="9" t="s">
         <v>259</v>
       </c>
@@ -5279,7 +5341,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="9" t="s">
         <v>263</v>
       </c>
@@ -5293,7 +5355,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="9" t="s">
         <v>267</v>
       </c>
@@ -5307,7 +5369,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="9" t="s">
         <v>271</v>
       </c>
@@ -5319,6 +5381,62 @@
       </c>
       <c r="D122" s="9" t="s">
         <v>274</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A123" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="D123" s="9" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="B124" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="C124" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="D124" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A125" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="B125" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="D125" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A126" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="B126" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="C126" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="D126" s="9" t="s">
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -5352,28 +5470,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5381,19 +5499,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="D2" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="12" t="n">
@@ -5406,22 +5524,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="D3" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="H3" s="12" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$H$2:$H$372,A3)</f>
@@ -5433,19 +5551,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="D4" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="12" t="n">
@@ -5458,19 +5576,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="D5" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G5" s="9"/>
       <c r="H5" s="12" t="n">
@@ -5483,22 +5601,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="D6" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="H6" s="12" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$H$2:$H$372,A6)</f>
@@ -5510,22 +5628,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="D7" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="H7" s="12" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$H$2:$H$372,A7)</f>
@@ -5537,19 +5655,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G8" s="9"/>
       <c r="H8" s="12" t="n">
@@ -5562,19 +5680,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="C9" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="D9" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>289</v>
-      </c>
       <c r="F9" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G9" s="9"/>
       <c r="H9" s="12" t="n">
@@ -5587,19 +5705,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="D10" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G10" s="9"/>
       <c r="H10" s="12" t="n">
@@ -5612,19 +5730,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="D11" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G11" s="9"/>
       <c r="H11" s="12" t="n">
@@ -5637,19 +5755,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="D12" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G12" s="9"/>
       <c r="H12" s="12" t="n">
@@ -5662,19 +5780,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="D13" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G13" s="9"/>
       <c r="H13" s="12" t="n">
@@ -5687,19 +5805,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="D14" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G14" s="9"/>
       <c r="H14" s="12" t="n">
@@ -5712,21 +5830,23 @@
         <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D15" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="G15" s="9"/>
+        <v>302</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>334</v>
+      </c>
       <c r="H15" s="12" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$H$2:$H$372,A15)</f>
         <v>27</v>
@@ -5737,19 +5857,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="D16" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G16" s="9"/>
       <c r="H16" s="12" t="n">
@@ -5762,19 +5882,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="D17" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G17" s="9"/>
       <c r="H17" s="12" t="n">
@@ -5787,19 +5907,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="D18" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G18" s="9"/>
       <c r="H18" s="12" t="n">
@@ -5812,19 +5932,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="C19" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="D19" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>308</v>
-      </c>
       <c r="F19" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G19" s="9"/>
       <c r="H19" s="12" t="n">
@@ -5837,19 +5957,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="D20" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G20" s="9"/>
       <c r="H20" s="12" t="n">
@@ -5862,22 +5982,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="D21" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>290</v>
+        <v>346</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="H21" s="12" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$H$2:$H$372,A21)</f>
@@ -5889,19 +6009,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="D22" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G22" s="9"/>
       <c r="H22" s="12" t="n">
@@ -5914,19 +6034,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="D23" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G23" s="9"/>
       <c r="H23" s="12" t="n">
@@ -5939,19 +6059,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="D24" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G24" s="9"/>
       <c r="H24" s="12" t="n">
@@ -5964,19 +6084,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="D25" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G25" s="9"/>
       <c r="H25" s="12" t="n">
@@ -5989,19 +6109,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="D26" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G26" s="9"/>
       <c r="H26" s="12" t="n">
@@ -6014,22 +6134,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="D27" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="H27" s="12" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$H$2:$H$372,A27)</f>
@@ -6041,19 +6161,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="D28" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G28" s="9"/>
       <c r="H28" s="12" t="n">
@@ -6066,19 +6186,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="D29" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G29" s="9"/>
       <c r="H29" s="12" t="n">
@@ -6091,22 +6211,22 @@
         <v>29</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="D30" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>290</v>
+        <v>346</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="H30" s="12" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$H$2:$H$372,A30)</f>
@@ -6118,19 +6238,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="D31" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G31" s="9"/>
       <c r="H31" s="12" t="n">
@@ -6143,19 +6263,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="D32" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G32" s="9"/>
       <c r="H32" s="12" t="n">
@@ -6168,19 +6288,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="D33" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G33" s="9"/>
       <c r="H33" s="12" t="n">
@@ -6193,19 +6313,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="D34" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G34" s="9"/>
       <c r="H34" s="12" t="n">
@@ -6218,19 +6338,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="D35" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G35" s="9"/>
       <c r="H35" s="12" t="n">
@@ -6243,19 +6363,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="D36" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G36" s="9"/>
       <c r="H36" s="12" t="n">
@@ -6268,19 +6388,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="D37" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G37" s="9"/>
       <c r="H37" s="12" t="n">
@@ -6293,19 +6413,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="D38" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G38" s="9"/>
       <c r="H38" s="12" t="n">
@@ -6318,22 +6438,22 @@
         <v>38</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="D39" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="H39" s="12" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$H$2:$H$372,A39)</f>
@@ -6345,22 +6465,22 @@
         <v>39</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="D40" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="H40" s="12" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$H$2:$H$372,A40)</f>
@@ -6372,19 +6492,19 @@
         <v>40</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="D41" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G41" s="9"/>
       <c r="H41" s="12" t="n">
@@ -6397,19 +6517,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="D42" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G42" s="9"/>
       <c r="H42" s="12" t="n">
@@ -6422,19 +6542,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="D43" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G43" s="9"/>
       <c r="H43" s="12" t="n">
@@ -6447,19 +6567,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="D44" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G44" s="9"/>
       <c r="H44" s="12" t="n">
@@ -6472,19 +6592,19 @@
         <v>44</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="D45" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G45" s="9"/>
       <c r="H45" s="12" t="n">
@@ -6497,22 +6617,22 @@
         <v>45</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="D46" s="13" t="n">
         <v>12</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="H46" s="12" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$H$2:$H$372,A46)</f>
@@ -6521,7 +6641,7 @@
     </row>
     <row r="48" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="14" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
@@ -6533,7 +6653,7 @@
     </row>
     <row r="49" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
@@ -6591,7 +6711,7 @@
         <v>40</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="C1" s="11" t="s">
         <v>41</v>
@@ -6606,40 +6726,40 @@
         <v>45</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="K1" s="11" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="M1" s="11" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="N1" s="11" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="R1" s="11" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6647,16 +6767,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="F2" s="16" t="n">
         <v>45874</v>
@@ -6703,16 +6823,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="F3" s="16" t="n">
         <v>45870</v>
@@ -6762,13 +6882,13 @@
         <v>50</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="F4" s="16" t="n">
         <v>38664</v>
@@ -6815,16 +6935,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="F5" s="16" t="n">
         <v>44970</v>
@@ -6874,13 +6994,13 @@
         <v>50</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="F6" s="16" t="n">
         <v>45720</v>
@@ -6930,13 +7050,13 @@
         <v>50</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="F7" s="16" t="n">
         <v>45908</v>
@@ -6983,16 +7103,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
       <c r="F8" s="16" t="n">
         <v>41365</v>
@@ -7039,16 +7159,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="F9" s="16" t="n">
         <v>46097</v>
@@ -7095,16 +7215,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="F10" s="16" t="n">
         <v>46266</v>
@@ -7151,16 +7271,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="F11" s="16" t="n">
         <v>46104</v>
@@ -7207,16 +7327,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="F12" s="16" t="n">
         <v>43283</v>
@@ -7263,16 +7383,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="F13" s="16" t="n">
         <v>46065</v>
@@ -7319,16 +7439,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="F14" s="16" t="n">
         <v>43845</v>
@@ -7375,16 +7495,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="F15" s="16" t="n">
         <v>39479</v>
@@ -7431,16 +7551,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="F16" s="16" t="n">
         <v>46237</v>
@@ -7487,16 +7607,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="F17" s="16" t="n">
         <v>45789</v>
@@ -7543,16 +7663,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="F18" s="16" t="n">
         <v>45429</v>
@@ -7581,7 +7701,7 @@
       </c>
       <c r="N18" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H18,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O18" s="17"/>
       <c r="P18" s="16" t="str">
@@ -7599,16 +7719,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="F19" s="16" t="n">
         <v>44327</v>
@@ -7637,7 +7757,7 @@
       </c>
       <c r="N19" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H19,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O19" s="17"/>
       <c r="P19" s="16" t="str">
@@ -7655,16 +7775,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="F20" s="16" t="n">
         <v>40087</v>
@@ -7711,16 +7831,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="F21" s="16" t="n">
         <v>40210</v>
@@ -7767,16 +7887,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>84</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="F22" s="16" t="n">
         <v>42438</v>
@@ -7823,16 +7943,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="D23" s="15" t="s">
         <v>84</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="F23" s="16" t="n">
         <v>45208</v>
@@ -7879,16 +7999,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="F24" s="16" t="n">
         <v>45950</v>
@@ -7937,16 +8057,16 @@
         <v>24</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="F25" s="16" t="n">
         <v>44152</v>
@@ -7993,16 +8113,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="F26" s="16" t="n">
         <v>41334</v>
@@ -8049,16 +8169,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="F27" s="16" t="n">
         <v>45957</v>
@@ -8105,16 +8225,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="F28" s="16" t="n">
         <v>45551</v>
@@ -8161,16 +8281,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="F29" s="16" t="n">
         <v>44092</v>
@@ -8217,16 +8337,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="F30" s="16" t="n">
         <v>46052</v>
@@ -8276,13 +8396,13 @@
         <v>81</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="F31" s="16" t="n">
         <v>45693</v>
@@ -8332,13 +8452,13 @@
         <v>81</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="F32" s="16" t="n">
         <v>45901</v>
@@ -8388,10 +8508,10 @@
         <v>81</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E33" s="15" t="s">
         <v>85</v>
@@ -8435,7 +8555,7 @@
         <v/>
       </c>
       <c r="R33" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8446,10 +8566,10 @@
         <v>81</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E34" s="15" t="s">
         <v>85</v>
@@ -8493,7 +8613,7 @@
         <v/>
       </c>
       <c r="R34" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8504,13 +8624,13 @@
         <v>81</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="F35" s="16" t="n">
         <v>46043</v>
@@ -8560,10 +8680,10 @@
         <v>81</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E36" s="15" t="s">
         <v>85</v>
@@ -8607,7 +8727,7 @@
         <v/>
       </c>
       <c r="R36" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8618,13 +8738,13 @@
         <v>81</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="F37" s="16" t="n">
         <v>45911</v>
@@ -8674,10 +8794,10 @@
         <v>81</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>456</v>
+        <v>474</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E38" s="15" t="s">
         <v>85</v>
@@ -8723,7 +8843,7 @@
         <v/>
       </c>
       <c r="R38" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8734,13 +8854,13 @@
         <v>81</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="F39" s="16" t="n">
         <v>45782</v>
@@ -8790,13 +8910,13 @@
         <v>81</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="D40" s="15" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="F40" s="16" t="n">
         <v>46073</v>
@@ -8848,13 +8968,13 @@
         <v>81</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="D41" s="15" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="F41" s="16" t="n">
         <v>45847</v>
@@ -8904,10 +9024,10 @@
         <v>81</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>460</v>
+        <v>478</v>
       </c>
       <c r="D42" s="15" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E42" s="15" t="s">
         <v>85</v>
@@ -8953,7 +9073,7 @@
         <v/>
       </c>
       <c r="R42" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8964,10 +9084,10 @@
         <v>81</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E43" s="15" t="s">
         <v>85</v>
@@ -9011,7 +9131,7 @@
         <v/>
       </c>
       <c r="R43" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9022,10 +9142,10 @@
         <v>81</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E44" s="15" t="s">
         <v>85</v>
@@ -9069,7 +9189,7 @@
         <v/>
       </c>
       <c r="R44" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9080,10 +9200,10 @@
         <v>81</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E45" s="15" t="s">
         <v>85</v>
@@ -9127,7 +9247,7 @@
         <v/>
       </c>
       <c r="R45" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9138,10 +9258,10 @@
         <v>81</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E46" s="15" t="s">
         <v>85</v>
@@ -9185,7 +9305,7 @@
         <v/>
       </c>
       <c r="R46" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9196,10 +9316,10 @@
         <v>81</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E47" s="15" t="s">
         <v>85</v>
@@ -9243,7 +9363,7 @@
         <v/>
       </c>
       <c r="R47" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9254,10 +9374,10 @@
         <v>81</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E48" s="15" t="s">
         <v>85</v>
@@ -9301,7 +9421,7 @@
         <v/>
       </c>
       <c r="R48" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9312,13 +9432,13 @@
         <v>81</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="F49" s="16" t="n">
         <v>45765</v>
@@ -9368,13 +9488,13 @@
         <v>81</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="F50" s="16" t="n">
         <v>45666</v>
@@ -9424,13 +9544,13 @@
         <v>81</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="F51" s="16" t="n">
         <v>46062</v>
@@ -9480,7 +9600,7 @@
         <v>81</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="D52" s="15" t="s">
         <v>75</v>
@@ -9527,7 +9647,7 @@
         <v/>
       </c>
       <c r="R52" s="9" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9538,10 +9658,10 @@
         <v>81</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>472</v>
+        <v>490</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E53" s="15" t="s">
         <v>80</v>
@@ -9573,7 +9693,7 @@
       </c>
       <c r="N53" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H53,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O53" s="17"/>
       <c r="P53" s="16" t="str">
@@ -9585,7 +9705,7 @@
         <v/>
       </c>
       <c r="R53" s="9" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9596,10 +9716,10 @@
         <v>81</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="E54" s="15" t="s">
         <v>80</v>
@@ -9631,7 +9751,7 @@
       </c>
       <c r="N54" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H54,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O54" s="17"/>
       <c r="P54" s="16" t="str">
@@ -9643,7 +9763,7 @@
         <v/>
       </c>
       <c r="R54" s="9" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9654,10 +9774,10 @@
         <v>81</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="E55" s="15" t="s">
         <v>80</v>
@@ -9691,7 +9811,7 @@
       </c>
       <c r="N55" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H55,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O55" s="17"/>
       <c r="P55" s="16" t="str">
@@ -9703,7 +9823,7 @@
         <v/>
       </c>
       <c r="R55" s="9" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9714,10 +9834,10 @@
         <v>81</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="E56" s="15" t="s">
         <v>80</v>
@@ -9749,7 +9869,7 @@
       </c>
       <c r="N56" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H56,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O56" s="17"/>
       <c r="P56" s="16" t="str">
@@ -9761,7 +9881,7 @@
         <v/>
       </c>
       <c r="R56" s="9" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9772,10 +9892,10 @@
         <v>81</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="E57" s="15" t="s">
         <v>80</v>
@@ -9809,7 +9929,7 @@
       </c>
       <c r="N57" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H57,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O57" s="17"/>
       <c r="P57" s="16" t="str">
@@ -9821,7 +9941,7 @@
         <v/>
       </c>
       <c r="R57" s="9" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9832,10 +9952,10 @@
         <v>81</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="E58" s="15" t="s">
         <v>80</v>
@@ -9867,7 +9987,7 @@
       </c>
       <c r="N58" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H58,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O58" s="17"/>
       <c r="P58" s="16" t="str">
@@ -9879,7 +9999,7 @@
         <v/>
       </c>
       <c r="R58" s="9" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9890,10 +10010,10 @@
         <v>81</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="E59" s="15" t="s">
         <v>80</v>
@@ -9925,7 +10045,7 @@
       </c>
       <c r="N59" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H59,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O59" s="17"/>
       <c r="P59" s="16" t="str">
@@ -9937,7 +10057,7 @@
         <v/>
       </c>
       <c r="R59" s="9" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9948,10 +10068,10 @@
         <v>81</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E60" s="15" t="s">
         <v>80</v>
@@ -9985,7 +10105,7 @@
       </c>
       <c r="N60" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H60,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O60" s="17"/>
       <c r="P60" s="16" t="str">
@@ -9997,7 +10117,7 @@
         <v/>
       </c>
       <c r="R60" s="9" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10008,13 +10128,13 @@
         <v>81</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="F61" s="16" t="n">
         <v>44124</v>
@@ -10045,7 +10165,7 @@
       </c>
       <c r="N61" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H61,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O61" s="17"/>
       <c r="P61" s="16" t="str">
@@ -10066,10 +10186,10 @@
         <v>81</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E62" s="15" t="s">
         <v>80</v>
@@ -10103,7 +10223,7 @@
       </c>
       <c r="N62" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H62,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O62" s="17"/>
       <c r="P62" s="16" t="str">
@@ -10115,7 +10235,7 @@
         <v/>
       </c>
       <c r="R62" s="9" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10126,10 +10246,10 @@
         <v>81</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E63" s="15" t="s">
         <v>80</v>
@@ -10163,7 +10283,7 @@
       </c>
       <c r="N63" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H63,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O63" s="17"/>
       <c r="P63" s="16" t="str">
@@ -10175,7 +10295,7 @@
         <v>ДА</v>
       </c>
       <c r="R63" s="9" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10186,10 +10306,10 @@
         <v>81</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E64" s="15" t="s">
         <v>80</v>
@@ -10223,7 +10343,7 @@
       </c>
       <c r="N64" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H64,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O64" s="17"/>
       <c r="P64" s="16" t="str">
@@ -10235,7 +10355,7 @@
         <v/>
       </c>
       <c r="R64" s="9" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10246,10 +10366,10 @@
         <v>81</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E65" s="15" t="s">
         <v>80</v>
@@ -10281,7 +10401,7 @@
       </c>
       <c r="N65" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H65,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O65" s="17"/>
       <c r="P65" s="16" t="str">
@@ -10293,7 +10413,7 @@
         <v/>
       </c>
       <c r="R65" s="9" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10304,10 +10424,10 @@
         <v>81</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E66" s="15" t="s">
         <v>80</v>
@@ -10341,7 +10461,7 @@
       </c>
       <c r="N66" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H66,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O66" s="17"/>
       <c r="P66" s="16" t="str">
@@ -10353,7 +10473,7 @@
         <v>ДА</v>
       </c>
       <c r="R66" s="9" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10364,10 +10484,10 @@
         <v>81</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E67" s="15" t="s">
         <v>80</v>
@@ -10401,7 +10521,7 @@
       </c>
       <c r="N67" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H67,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O67" s="17"/>
       <c r="P67" s="16" t="str">
@@ -10413,7 +10533,7 @@
         <v/>
       </c>
       <c r="R67" s="9" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10424,13 +10544,13 @@
         <v>81</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="F68" s="16" t="n">
         <v>45782</v>
@@ -10480,7 +10600,7 @@
         <v>81</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="D69" s="15" t="s">
         <v>84</v>
@@ -10527,7 +10647,7 @@
         <v/>
       </c>
       <c r="R69" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10538,7 +10658,7 @@
         <v>81</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="D70" s="15" t="s">
         <v>84</v>
@@ -10585,7 +10705,7 @@
         <v/>
       </c>
       <c r="R70" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10596,13 +10716,13 @@
         <v>81</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="F71" s="16" t="n">
         <v>45425</v>
@@ -10654,13 +10774,13 @@
         <v>81</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="F72" s="16" t="n">
         <v>44368</v>
@@ -10710,7 +10830,7 @@
         <v>81</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="D73" s="15" t="s">
         <v>84</v>
@@ -10757,7 +10877,7 @@
         <v/>
       </c>
       <c r="R73" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10768,7 +10888,7 @@
         <v>81</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="D74" s="15" t="s">
         <v>84</v>
@@ -10815,7 +10935,7 @@
         <v/>
       </c>
       <c r="R74" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10826,7 +10946,7 @@
         <v>81</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="D75" s="15" t="s">
         <v>84</v>
@@ -10873,7 +10993,7 @@
         <v/>
       </c>
       <c r="R75" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10884,7 +11004,7 @@
         <v>81</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="D76" s="15" t="s">
         <v>84</v>
@@ -10933,7 +11053,7 @@
         <v/>
       </c>
       <c r="R76" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10944,7 +11064,7 @@
         <v>81</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="D77" s="15" t="s">
         <v>84</v>
@@ -10991,7 +11111,7 @@
         <v/>
       </c>
       <c r="R77" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11002,7 +11122,7 @@
         <v>81</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>500</v>
+        <v>518</v>
       </c>
       <c r="D78" s="15" t="s">
         <v>84</v>
@@ -11049,7 +11169,7 @@
         <v/>
       </c>
       <c r="R78" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11060,7 +11180,7 @@
         <v>81</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>501</v>
+        <v>519</v>
       </c>
       <c r="D79" s="15" t="s">
         <v>84</v>
@@ -11107,7 +11227,7 @@
         <v/>
       </c>
       <c r="R79" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11118,7 +11238,7 @@
         <v>81</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>502</v>
+        <v>520</v>
       </c>
       <c r="D80" s="15" t="s">
         <v>84</v>
@@ -11165,7 +11285,7 @@
         <v/>
       </c>
       <c r="R80" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11176,7 +11296,7 @@
         <v>81</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>503</v>
+        <v>521</v>
       </c>
       <c r="D81" s="15" t="s">
         <v>84</v>
@@ -11223,7 +11343,7 @@
         <v/>
       </c>
       <c r="R81" s="9" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11234,13 +11354,13 @@
         <v>81</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>504</v>
+        <v>522</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>505</v>
+        <v>523</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="F82" s="16" t="n">
         <v>42121</v>
@@ -11290,7 +11410,7 @@
         <v>81</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
       <c r="D83" s="15" t="s">
         <v>60</v>
@@ -11337,7 +11457,7 @@
         <v/>
       </c>
       <c r="R83" s="9" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11348,7 +11468,7 @@
         <v>81</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>508</v>
+        <v>526</v>
       </c>
       <c r="D84" s="15" t="s">
         <v>60</v>
@@ -11397,7 +11517,7 @@
         <v/>
       </c>
       <c r="R84" s="9" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11408,7 +11528,7 @@
         <v>81</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>509</v>
+        <v>527</v>
       </c>
       <c r="D85" s="15" t="s">
         <v>60</v>
@@ -11455,7 +11575,7 @@
         <v/>
       </c>
       <c r="R85" s="9" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11466,13 +11586,13 @@
         <v>81</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="F86" s="16" t="n">
         <v>42983</v>
@@ -11503,7 +11623,7 @@
       </c>
       <c r="N86" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H86,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O86" s="17"/>
       <c r="P86" s="16" t="str">
@@ -11524,13 +11644,13 @@
         <v>81</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>512</v>
+        <v>530</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>513</v>
+        <v>531</v>
       </c>
       <c r="F87" s="16" t="n">
         <v>44966</v>
@@ -11571,7 +11691,7 @@
         <v/>
       </c>
       <c r="R87" s="9" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11582,13 +11702,13 @@
         <v>50</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="F88" s="16" t="n">
         <v>46139</v>
@@ -11638,13 +11758,13 @@
         <v>72</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="E89" s="15" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F89" s="16" t="n">
         <v>45558</v>
@@ -11694,13 +11814,13 @@
         <v>50</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="E90" s="15" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F90" s="16" t="n">
         <v>43031</v>
@@ -11750,13 +11870,13 @@
         <v>50</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="E91" s="15" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F91" s="16" t="n">
         <v>45719</v>
@@ -11806,13 +11926,13 @@
         <v>50</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="D92" s="15" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F92" s="16" t="n">
         <v>45803</v>
@@ -11862,13 +11982,13 @@
         <v>50</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>524</v>
+        <v>542</v>
       </c>
       <c r="D93" s="15" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="E93" s="15" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F93" s="16" t="n">
         <v>45833</v>
@@ -11918,13 +12038,13 @@
         <v>50</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>525</v>
+        <v>543</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="E94" s="15" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F94" s="16" t="n">
         <v>45908</v>
@@ -11974,13 +12094,13 @@
         <v>50</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>526</v>
+        <v>544</v>
       </c>
       <c r="D95" s="15" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="E95" s="15" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F95" s="16" t="n">
         <v>42360</v>
@@ -12030,13 +12150,13 @@
         <v>50</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="D96" s="15" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F96" s="16" t="n">
         <v>45966</v>
@@ -12086,13 +12206,13 @@
         <v>50</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>528</v>
+        <v>546</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="E97" s="15" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F97" s="16" t="n">
         <v>46113</v>
@@ -12142,13 +12262,13 @@
         <v>50</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
       <c r="D98" s="15" t="s">
         <v>95</v>
       </c>
       <c r="E98" s="15" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F98" s="16" t="n">
         <v>45691</v>
@@ -12198,13 +12318,13 @@
         <v>50</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="D99" s="15" t="s">
         <v>95</v>
       </c>
       <c r="E99" s="15" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F99" s="16" t="n">
         <v>45537</v>
@@ -12254,13 +12374,13 @@
         <v>50</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>531</v>
+        <v>549</v>
       </c>
       <c r="D100" s="15" t="s">
         <v>95</v>
       </c>
       <c r="E100" s="15" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F100" s="16" t="n">
         <v>45579</v>
@@ -12310,13 +12430,13 @@
         <v>50</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>532</v>
+        <v>550</v>
       </c>
       <c r="D101" s="15" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="E101" s="15" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F101" s="16" t="n">
         <v>40616</v>
@@ -12366,13 +12486,13 @@
         <v>50</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="F102" s="16" t="n">
         <v>45397</v>
@@ -12422,13 +12542,13 @@
         <v>50</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>536</v>
+        <v>554</v>
       </c>
       <c r="D103" s="15" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="F103" s="16" t="n">
         <v>45509</v>
@@ -12478,13 +12598,13 @@
         <v>50</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>539</v>
+        <v>557</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="E104" s="15" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="F104" s="16" t="n">
         <v>45565</v>
@@ -12534,13 +12654,13 @@
         <v>50</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="D105" s="15" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="E105" s="15" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="F105" s="16" t="n">
         <v>45924</v>
@@ -12592,13 +12712,13 @@
         <v>50</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="D106" s="15" t="s">
         <v>99</v>
       </c>
       <c r="E106" s="15" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="F106" s="16" t="n">
         <v>45638</v>
@@ -12648,13 +12768,13 @@
         <v>50</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>542</v>
+        <v>560</v>
       </c>
       <c r="D107" s="15" t="s">
         <v>99</v>
       </c>
       <c r="E107" s="15" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="F107" s="16" t="n">
         <v>45792</v>
@@ -12704,10 +12824,10 @@
         <v>50</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="D108" s="15" t="s">
-        <v>544</v>
+        <v>562</v>
       </c>
       <c r="E108" s="15" t="s">
         <v>61</v>
@@ -12760,7 +12880,7 @@
         <v>50</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>545</v>
+        <v>563</v>
       </c>
       <c r="D109" s="15" t="s">
         <v>60</v>
@@ -12816,13 +12936,13 @@
         <v>50</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>546</v>
+        <v>564</v>
       </c>
       <c r="D110" s="15" t="s">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="E110" s="15" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="F110" s="16" t="n">
         <v>45691</v>
@@ -12872,13 +12992,13 @@
         <v>50</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>548</v>
+        <v>566</v>
       </c>
       <c r="D111" s="15" t="s">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="E111" s="15" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="F111" s="16" t="n">
         <v>45930</v>
@@ -12930,13 +13050,13 @@
         <v>50</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="D112" s="15" t="s">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="E112" s="15" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="F112" s="16" t="n">
         <v>45840</v>
@@ -12988,10 +13108,10 @@
         <v>50</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
       <c r="D113" s="15" t="s">
-        <v>552</v>
+        <v>570</v>
       </c>
       <c r="E113" s="15" t="s">
         <v>61</v>
@@ -13044,10 +13164,10 @@
         <v>50</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>553</v>
+        <v>571</v>
       </c>
       <c r="D114" s="15" t="s">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="E114" s="15" t="s">
         <v>191</v>
@@ -13091,7 +13211,7 @@
         <v/>
       </c>
       <c r="R114" s="9" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13102,10 +13222,10 @@
         <v>50</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>556</v>
+        <v>574</v>
       </c>
       <c r="D115" s="15" t="s">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="E115" s="15" t="s">
         <v>191</v>
@@ -13149,7 +13269,7 @@
         <v/>
       </c>
       <c r="R115" s="9" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13160,10 +13280,10 @@
         <v>50</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>557</v>
+        <v>575</v>
       </c>
       <c r="D116" s="15" t="s">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="E116" s="15" t="s">
         <v>191</v>
@@ -13207,7 +13327,7 @@
         <v/>
       </c>
       <c r="R116" s="9" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13218,10 +13338,10 @@
         <v>50</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>558</v>
+        <v>576</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="E117" s="15" t="s">
         <v>191</v>
@@ -13265,7 +13385,7 @@
         <v/>
       </c>
       <c r="R117" s="9" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13276,10 +13396,10 @@
         <v>50</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>559</v>
+        <v>577</v>
       </c>
       <c r="D118" s="15" t="s">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="E118" s="15" t="s">
         <v>191</v>
@@ -13323,7 +13443,7 @@
         <v/>
       </c>
       <c r="R118" s="9" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13334,10 +13454,10 @@
         <v>50</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="D119" s="15" t="s">
-        <v>561</v>
+        <v>579</v>
       </c>
       <c r="E119" s="15" t="s">
         <v>191</v>
@@ -13381,7 +13501,7 @@
         <v/>
       </c>
       <c r="R119" s="9" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13392,10 +13512,10 @@
         <v>50</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>562</v>
+        <v>580</v>
       </c>
       <c r="D120" s="15" t="s">
-        <v>561</v>
+        <v>579</v>
       </c>
       <c r="E120" s="15" t="s">
         <v>191</v>
@@ -13439,7 +13559,7 @@
         <v/>
       </c>
       <c r="R120" s="9" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13450,10 +13570,10 @@
         <v>50</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>563</v>
+        <v>581</v>
       </c>
       <c r="D121" s="15" t="s">
-        <v>561</v>
+        <v>579</v>
       </c>
       <c r="E121" s="15" t="s">
         <v>191</v>
@@ -13497,7 +13617,7 @@
         <v/>
       </c>
       <c r="R121" s="9" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13508,13 +13628,13 @@
         <v>50</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>564</v>
+        <v>582</v>
       </c>
       <c r="D122" s="15" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="E122" s="15" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="F122" s="16" t="n">
         <v>45362</v>
@@ -13564,13 +13684,13 @@
         <v>50</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>565</v>
+        <v>583</v>
       </c>
       <c r="D123" s="15" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="F123" s="16" t="n">
         <v>45917</v>
@@ -13620,13 +13740,13 @@
         <v>50</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>566</v>
+        <v>584</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="E124" s="15" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="F124" s="16" t="n">
         <v>45922</v>
@@ -13676,13 +13796,13 @@
         <v>50</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>567</v>
+        <v>585</v>
       </c>
       <c r="D125" s="15" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="E125" s="15" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="F125" s="16" t="n">
         <v>45454</v>
@@ -13732,10 +13852,10 @@
         <v>50</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>568</v>
+        <v>586</v>
       </c>
       <c r="D126" s="15" t="s">
-        <v>569</v>
+        <v>587</v>
       </c>
       <c r="E126" s="15" t="s">
         <v>191</v>
@@ -13779,7 +13899,7 @@
         <v/>
       </c>
       <c r="R126" s="9" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13790,10 +13910,10 @@
         <v>50</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>570</v>
+        <v>588</v>
       </c>
       <c r="D127" s="15" t="s">
-        <v>569</v>
+        <v>587</v>
       </c>
       <c r="E127" s="15" t="s">
         <v>191</v>
@@ -13837,7 +13957,7 @@
         <v/>
       </c>
       <c r="R127" s="9" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13848,10 +13968,10 @@
         <v>50</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>571</v>
+        <v>589</v>
       </c>
       <c r="D128" s="15" t="s">
-        <v>569</v>
+        <v>587</v>
       </c>
       <c r="E128" s="15" t="s">
         <v>191</v>
@@ -13895,7 +14015,7 @@
         <v/>
       </c>
       <c r="R128" s="9" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13906,10 +14026,10 @@
         <v>50</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>572</v>
+        <v>590</v>
       </c>
       <c r="D129" s="15" t="s">
-        <v>569</v>
+        <v>587</v>
       </c>
       <c r="E129" s="15" t="s">
         <v>191</v>
@@ -13953,7 +14073,7 @@
         <v/>
       </c>
       <c r="R129" s="9" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13964,13 +14084,13 @@
         <v>50</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="D130" s="15" t="s">
         <v>60</v>
       </c>
       <c r="E130" s="15" t="s">
-        <v>574</v>
+        <v>592</v>
       </c>
       <c r="F130" s="16" t="n">
         <v>46132</v>
@@ -14025,10 +14145,10 @@
         <v>108</v>
       </c>
       <c r="D131" s="15" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E131" s="15" t="s">
-        <v>574</v>
+        <v>592</v>
       </c>
       <c r="F131" s="16" t="n">
         <v>45846</v>
@@ -14059,7 +14179,7 @@
       </c>
       <c r="N131" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H131,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O131" s="17"/>
       <c r="P131" s="16" t="str">
@@ -14085,10 +14205,10 @@
         <v>110</v>
       </c>
       <c r="D132" s="15" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E132" s="15" t="s">
-        <v>574</v>
+        <v>592</v>
       </c>
       <c r="F132" s="16" t="n">
         <v>45958</v>
@@ -14117,7 +14237,7 @@
       </c>
       <c r="N132" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H132,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O132" s="17"/>
       <c r="P132" s="16" t="str">
@@ -14143,10 +14263,10 @@
         <v>111</v>
       </c>
       <c r="D133" s="15" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E133" s="15" t="s">
-        <v>575</v>
+        <v>593</v>
       </c>
       <c r="F133" s="16" t="n">
         <v>43313</v>
@@ -14175,7 +14295,7 @@
       </c>
       <c r="N133" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H133,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O133" s="17"/>
       <c r="P133" s="16" t="str">
@@ -14201,10 +14321,10 @@
         <v>112</v>
       </c>
       <c r="D134" s="15" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E134" s="15" t="s">
-        <v>575</v>
+        <v>593</v>
       </c>
       <c r="F134" s="16" t="n">
         <v>42289</v>
@@ -14233,7 +14353,7 @@
       </c>
       <c r="N134" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H134,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O134" s="17"/>
       <c r="P134" s="16" t="str">
@@ -14259,7 +14379,7 @@
         <v>113</v>
       </c>
       <c r="D135" s="15" t="s">
-        <v>576</v>
+        <v>594</v>
       </c>
       <c r="E135" s="15" t="s">
         <v>49</v>
@@ -14317,7 +14437,7 @@
         <v>115</v>
       </c>
       <c r="D136" s="15" t="s">
-        <v>576</v>
+        <v>594</v>
       </c>
       <c r="E136" s="15" t="s">
         <v>49</v>
@@ -14375,7 +14495,7 @@
         <v>116</v>
       </c>
       <c r="D137" s="15" t="s">
-        <v>576</v>
+        <v>594</v>
       </c>
       <c r="E137" s="15" t="s">
         <v>182</v>
@@ -14488,10 +14608,10 @@
         <v>50</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>577</v>
+        <v>595</v>
       </c>
       <c r="D139" s="15" t="s">
-        <v>578</v>
+        <v>596</v>
       </c>
       <c r="E139" s="15" t="s">
         <v>182</v>
@@ -14602,7 +14722,7 @@
         <v>50</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>579</v>
+        <v>597</v>
       </c>
       <c r="D141" s="15" t="s">
         <v>64</v>
@@ -14649,7 +14769,7 @@
         <v/>
       </c>
       <c r="R141" s="9" t="s">
-        <v>580</v>
+        <v>598</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14660,7 +14780,7 @@
         <v>50</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>581</v>
+        <v>599</v>
       </c>
       <c r="D142" s="15" t="s">
         <v>60</v>
@@ -14716,7 +14836,7 @@
         <v>50</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>582</v>
+        <v>600</v>
       </c>
       <c r="D143" s="15" t="s">
         <v>60</v>
@@ -14772,10 +14892,10 @@
         <v>50</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>583</v>
+        <v>601</v>
       </c>
       <c r="D144" s="15" t="s">
-        <v>584</v>
+        <v>602</v>
       </c>
       <c r="E144" s="15" t="s">
         <v>49</v>
@@ -14819,7 +14939,7 @@
         <v/>
       </c>
       <c r="R144" s="9" t="s">
-        <v>585</v>
+        <v>603</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14833,7 +14953,7 @@
         <v>120</v>
       </c>
       <c r="D145" s="15" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="E145" s="15" t="s">
         <v>49</v>
@@ -14891,7 +15011,7 @@
         <v>122</v>
       </c>
       <c r="D146" s="15" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="E146" s="15" t="s">
         <v>182</v>
@@ -14949,7 +15069,7 @@
         <v>123</v>
       </c>
       <c r="D147" s="15" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="E147" s="15" t="s">
         <v>49</v>
@@ -15007,7 +15127,7 @@
         <v>124</v>
       </c>
       <c r="D148" s="15" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="E148" s="15" t="s">
         <v>182</v>
@@ -15065,7 +15185,7 @@
         <v>125</v>
       </c>
       <c r="D149" s="15" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="E149" s="15" t="s">
         <v>49</v>
@@ -15123,7 +15243,7 @@
         <v>126</v>
       </c>
       <c r="D150" s="15" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="E150" s="15" t="s">
         <v>49</v>
@@ -15181,7 +15301,7 @@
         <v>127</v>
       </c>
       <c r="D151" s="15" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="E151" s="15" t="s">
         <v>49</v>
@@ -15239,7 +15359,7 @@
         <v>128</v>
       </c>
       <c r="D152" s="15" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="E152" s="15" t="s">
         <v>49</v>
@@ -15297,7 +15417,7 @@
         <v>129</v>
       </c>
       <c r="D153" s="15" t="s">
-        <v>587</v>
+        <v>605</v>
       </c>
       <c r="E153" s="15" t="s">
         <v>49</v>
@@ -15355,7 +15475,7 @@
         <v>131</v>
       </c>
       <c r="D154" s="15" t="s">
-        <v>587</v>
+        <v>605</v>
       </c>
       <c r="E154" s="15" t="s">
         <v>49</v>
@@ -15413,7 +15533,7 @@
         <v>132</v>
       </c>
       <c r="D155" s="15" t="s">
-        <v>587</v>
+        <v>605</v>
       </c>
       <c r="E155" s="15" t="s">
         <v>49</v>
@@ -15471,7 +15591,7 @@
         <v>133</v>
       </c>
       <c r="D156" s="15" t="s">
-        <v>587</v>
+        <v>605</v>
       </c>
       <c r="E156" s="15" t="s">
         <v>182</v>
@@ -15529,7 +15649,7 @@
         <v>134</v>
       </c>
       <c r="D157" s="15" t="s">
-        <v>587</v>
+        <v>605</v>
       </c>
       <c r="E157" s="15" t="s">
         <v>49</v>
@@ -15587,7 +15707,7 @@
         <v>135</v>
       </c>
       <c r="D158" s="15" t="s">
-        <v>587</v>
+        <v>605</v>
       </c>
       <c r="E158" s="15" t="s">
         <v>182</v>
@@ -15645,7 +15765,7 @@
         <v>136</v>
       </c>
       <c r="D159" s="15" t="s">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="E159" s="15" t="s">
         <v>182</v>
@@ -15703,7 +15823,7 @@
         <v>138</v>
       </c>
       <c r="D160" s="15" t="s">
-        <v>587</v>
+        <v>605</v>
       </c>
       <c r="E160" s="15" t="s">
         <v>49</v>
@@ -15758,10 +15878,10 @@
         <v>50</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>589</v>
+        <v>607</v>
       </c>
       <c r="D161" s="15" t="s">
-        <v>590</v>
+        <v>608</v>
       </c>
       <c r="E161" s="15" t="s">
         <v>49</v>
@@ -15817,7 +15937,7 @@
         <v>139</v>
       </c>
       <c r="D162" s="15" t="s">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="E162" s="15" t="s">
         <v>182</v>
@@ -15872,7 +15992,7 @@
         <v>50</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>591</v>
+        <v>609</v>
       </c>
       <c r="D163" s="15" t="s">
         <v>48</v>
@@ -15928,7 +16048,7 @@
         <v>50</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>592</v>
+        <v>610</v>
       </c>
       <c r="D164" s="15" t="s">
         <v>48</v>
@@ -15986,10 +16106,10 @@
         <v>50</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>593</v>
+        <v>611</v>
       </c>
       <c r="D165" s="15" t="s">
-        <v>594</v>
+        <v>612</v>
       </c>
       <c r="E165" s="15" t="s">
         <v>49</v>
@@ -16042,10 +16162,10 @@
         <v>50</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>595</v>
+        <v>613</v>
       </c>
       <c r="D166" s="15" t="s">
-        <v>594</v>
+        <v>612</v>
       </c>
       <c r="E166" s="15" t="s">
         <v>49</v>
@@ -16098,10 +16218,10 @@
         <v>50</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>596</v>
+        <v>614</v>
       </c>
       <c r="D167" s="15" t="s">
-        <v>597</v>
+        <v>615</v>
       </c>
       <c r="E167" s="15" t="s">
         <v>49</v>
@@ -16154,10 +16274,10 @@
         <v>50</v>
       </c>
       <c r="C168" s="15" t="s">
-        <v>598</v>
+        <v>616</v>
       </c>
       <c r="D168" s="15" t="s">
-        <v>597</v>
+        <v>615</v>
       </c>
       <c r="E168" s="15" t="s">
         <v>182</v>
@@ -16268,10 +16388,10 @@
         <v>50</v>
       </c>
       <c r="C170" s="15" t="s">
-        <v>599</v>
+        <v>617</v>
       </c>
       <c r="D170" s="15" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="E170" s="15" t="s">
         <v>49</v>
@@ -16324,10 +16444,10 @@
         <v>50</v>
       </c>
       <c r="C171" s="15" t="s">
-        <v>600</v>
+        <v>618</v>
       </c>
       <c r="D171" s="15" t="s">
-        <v>601</v>
+        <v>619</v>
       </c>
       <c r="E171" s="15" t="s">
         <v>182</v>
@@ -16383,7 +16503,7 @@
         <v>143</v>
       </c>
       <c r="D172" s="15" t="s">
-        <v>602</v>
+        <v>620</v>
       </c>
       <c r="E172" s="15" t="s">
         <v>182</v>
@@ -16438,10 +16558,10 @@
         <v>50</v>
       </c>
       <c r="C173" s="15" t="s">
-        <v>603</v>
+        <v>621</v>
       </c>
       <c r="D173" s="15" t="s">
-        <v>601</v>
+        <v>619</v>
       </c>
       <c r="E173" s="15" t="s">
         <v>49</v>
@@ -16494,10 +16614,10 @@
         <v>50</v>
       </c>
       <c r="C174" s="15" t="s">
-        <v>604</v>
+        <v>622</v>
       </c>
       <c r="D174" s="15" t="s">
-        <v>601</v>
+        <v>619</v>
       </c>
       <c r="E174" s="15" t="s">
         <v>49</v>
@@ -16553,7 +16673,7 @@
         <v>145</v>
       </c>
       <c r="D175" s="15" t="s">
-        <v>605</v>
+        <v>623</v>
       </c>
       <c r="E175" s="15" t="s">
         <v>182</v>
@@ -16610,7 +16730,7 @@
         <v>50</v>
       </c>
       <c r="C176" s="15" t="s">
-        <v>606</v>
+        <v>624</v>
       </c>
       <c r="D176" s="15" t="s">
         <v>60</v>
@@ -16669,7 +16789,7 @@
         <v>147</v>
       </c>
       <c r="D177" s="15" t="s">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="E177" s="15" t="s">
         <v>187</v>
@@ -16727,7 +16847,7 @@
         <v>149</v>
       </c>
       <c r="D178" s="15" t="s">
-        <v>588</v>
+        <v>606</v>
       </c>
       <c r="E178" s="15" t="s">
         <v>187</v>
@@ -16785,7 +16905,7 @@
         <v>150</v>
       </c>
       <c r="D179" s="15" t="s">
-        <v>607</v>
+        <v>625</v>
       </c>
       <c r="E179" s="15" t="s">
         <v>57</v>
@@ -16843,7 +16963,7 @@
         <v>152</v>
       </c>
       <c r="D180" s="15" t="s">
-        <v>607</v>
+        <v>625</v>
       </c>
       <c r="E180" s="15" t="s">
         <v>187</v>
@@ -16901,7 +17021,7 @@
         <v>153</v>
       </c>
       <c r="D181" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="E181" s="15" t="s">
         <v>187</v>
@@ -16956,10 +17076,10 @@
         <v>50</v>
       </c>
       <c r="C182" s="15" t="s">
-        <v>609</v>
+        <v>627</v>
       </c>
       <c r="D182" s="15" t="s">
-        <v>610</v>
+        <v>628</v>
       </c>
       <c r="E182" s="15" t="s">
         <v>187</v>
@@ -17015,7 +17135,7 @@
         <v>155</v>
       </c>
       <c r="D183" s="15" t="s">
-        <v>597</v>
+        <v>615</v>
       </c>
       <c r="E183" s="15" t="s">
         <v>57</v>
@@ -17070,10 +17190,10 @@
         <v>50</v>
       </c>
       <c r="C184" s="15" t="s">
-        <v>611</v>
+        <v>629</v>
       </c>
       <c r="D184" s="15" t="s">
-        <v>612</v>
+        <v>630</v>
       </c>
       <c r="E184" s="15" t="s">
         <v>57</v>
@@ -17128,10 +17248,10 @@
         <v>50</v>
       </c>
       <c r="C185" s="15" t="s">
-        <v>613</v>
+        <v>631</v>
       </c>
       <c r="D185" s="15" t="s">
-        <v>612</v>
+        <v>630</v>
       </c>
       <c r="E185" s="15" t="s">
         <v>57</v>
@@ -17187,7 +17307,7 @@
         <v>157</v>
       </c>
       <c r="D186" s="15" t="s">
-        <v>614</v>
+        <v>632</v>
       </c>
       <c r="E186" s="15" t="s">
         <v>187</v>
@@ -17245,7 +17365,7 @@
         <v>159</v>
       </c>
       <c r="D187" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="E187" s="15" t="s">
         <v>57</v>
@@ -17303,7 +17423,7 @@
         <v>161</v>
       </c>
       <c r="D188" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="E188" s="15" t="s">
         <v>57</v>
@@ -17361,7 +17481,7 @@
         <v>162</v>
       </c>
       <c r="D189" s="15" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="E189" s="15" t="s">
         <v>57</v>
@@ -17419,7 +17539,7 @@
         <v>163</v>
       </c>
       <c r="D190" s="15" t="s">
-        <v>615</v>
+        <v>633</v>
       </c>
       <c r="E190" s="15" t="s">
         <v>187</v>
@@ -17477,7 +17597,7 @@
         <v>165</v>
       </c>
       <c r="D191" s="15" t="s">
-        <v>615</v>
+        <v>633</v>
       </c>
       <c r="E191" s="15" t="s">
         <v>187</v>
@@ -17713,7 +17833,7 @@
         <v>170</v>
       </c>
       <c r="D195" s="15" t="s">
-        <v>616</v>
+        <v>634</v>
       </c>
       <c r="E195" s="15" t="s">
         <v>57</v>
@@ -17768,13 +17888,13 @@
         <v>50</v>
       </c>
       <c r="C196" s="15" t="s">
-        <v>617</v>
+        <v>635</v>
       </c>
       <c r="D196" s="15" t="s">
-        <v>618</v>
+        <v>636</v>
       </c>
       <c r="E196" s="15" t="s">
-        <v>619</v>
+        <v>637</v>
       </c>
       <c r="F196" s="16" t="n">
         <v>45649</v>
@@ -17824,13 +17944,13 @@
         <v>50</v>
       </c>
       <c r="C197" s="15" t="s">
-        <v>620</v>
+        <v>638</v>
       </c>
       <c r="D197" s="15" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="E197" s="15" t="s">
-        <v>621</v>
+        <v>639</v>
       </c>
       <c r="F197" s="16" t="n">
         <v>45943</v>
@@ -17880,13 +18000,13 @@
         <v>50</v>
       </c>
       <c r="C198" s="15" t="s">
-        <v>622</v>
+        <v>640</v>
       </c>
       <c r="D198" s="15" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="E198" s="15" t="s">
-        <v>621</v>
+        <v>639</v>
       </c>
       <c r="F198" s="16" t="n">
         <v>46077</v>
@@ -17936,13 +18056,13 @@
         <v>50</v>
       </c>
       <c r="C199" s="15" t="s">
-        <v>623</v>
+        <v>641</v>
       </c>
       <c r="D199" s="15" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="E199" s="15" t="s">
-        <v>621</v>
+        <v>639</v>
       </c>
       <c r="F199" s="16" t="n">
         <v>46097</v>
@@ -17992,13 +18112,13 @@
         <v>50</v>
       </c>
       <c r="C200" s="15" t="s">
-        <v>624</v>
+        <v>642</v>
       </c>
       <c r="D200" s="15" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="E200" s="15" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="F200" s="16" t="n">
         <v>43040</v>
@@ -18048,13 +18168,13 @@
         <v>50</v>
       </c>
       <c r="C201" s="15" t="s">
-        <v>626</v>
+        <v>644</v>
       </c>
       <c r="D201" s="15" t="s">
-        <v>618</v>
+        <v>636</v>
       </c>
       <c r="E201" s="15" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="F201" s="16" t="n">
         <v>46080</v>
@@ -18104,13 +18224,13 @@
         <v>50</v>
       </c>
       <c r="C202" s="15" t="s">
-        <v>627</v>
+        <v>645</v>
       </c>
       <c r="D202" s="15" t="s">
-        <v>618</v>
+        <v>636</v>
       </c>
       <c r="E202" s="15" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="F202" s="16" t="n">
         <v>46111</v>
@@ -18160,13 +18280,13 @@
         <v>50</v>
       </c>
       <c r="C203" s="15" t="s">
-        <v>628</v>
+        <v>646</v>
       </c>
       <c r="D203" s="15" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="E203" s="15" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="F203" s="16" t="n">
         <v>46064</v>
@@ -18216,13 +18336,13 @@
         <v>50</v>
       </c>
       <c r="C204" s="15" t="s">
-        <v>629</v>
+        <v>647</v>
       </c>
       <c r="D204" s="15" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="E204" s="15" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="F204" s="16" t="n">
         <v>46049</v>
@@ -18272,13 +18392,13 @@
         <v>50</v>
       </c>
       <c r="C205" s="15" t="s">
-        <v>630</v>
+        <v>648</v>
       </c>
       <c r="D205" s="15" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="E205" s="15" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="F205" s="16" t="n">
         <v>45748</v>
@@ -18328,13 +18448,13 @@
         <v>50</v>
       </c>
       <c r="C206" s="15" t="s">
-        <v>631</v>
+        <v>649</v>
       </c>
       <c r="D206" s="15" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="E206" s="15" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="F206" s="16" t="n">
         <v>46091</v>
@@ -18384,13 +18504,13 @@
         <v>50</v>
       </c>
       <c r="C207" s="15" t="s">
-        <v>632</v>
+        <v>650</v>
       </c>
       <c r="D207" s="15" t="s">
-        <v>633</v>
+        <v>651</v>
       </c>
       <c r="E207" s="15" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="F207" s="16" t="n">
         <v>44621</v>
@@ -18440,13 +18560,13 @@
         <v>50</v>
       </c>
       <c r="C208" s="15" t="s">
-        <v>634</v>
+        <v>652</v>
       </c>
       <c r="D208" s="15" t="s">
-        <v>633</v>
+        <v>651</v>
       </c>
       <c r="E208" s="15" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="F208" s="16" t="n">
         <v>46084</v>
@@ -18496,13 +18616,13 @@
         <v>50</v>
       </c>
       <c r="C209" s="15" t="s">
-        <v>635</v>
+        <v>653</v>
       </c>
       <c r="D209" s="15" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="E209" s="15" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="F209" s="16" t="n">
         <v>45596</v>
@@ -18552,13 +18672,13 @@
         <v>50</v>
       </c>
       <c r="C210" s="15" t="s">
-        <v>636</v>
+        <v>654</v>
       </c>
       <c r="D210" s="15" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
       <c r="E210" s="15" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="F210" s="16" t="n">
         <v>46036</v>
@@ -18608,13 +18728,13 @@
         <v>50</v>
       </c>
       <c r="C211" s="15" t="s">
-        <v>638</v>
+        <v>656</v>
       </c>
       <c r="D211" s="15" t="s">
-        <v>639</v>
+        <v>657</v>
       </c>
       <c r="E211" s="15" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="F211" s="16" t="n">
         <v>42388</v>
@@ -18664,13 +18784,13 @@
         <v>50</v>
       </c>
       <c r="C212" s="15" t="s">
-        <v>640</v>
+        <v>658</v>
       </c>
       <c r="D212" s="15" t="s">
-        <v>641</v>
+        <v>659</v>
       </c>
       <c r="E212" s="15" t="s">
-        <v>625</v>
+        <v>643</v>
       </c>
       <c r="F212" s="16" t="n">
         <v>45817</v>
@@ -18720,13 +18840,13 @@
         <v>50</v>
       </c>
       <c r="C213" s="15" t="s">
-        <v>642</v>
+        <v>660</v>
       </c>
       <c r="D213" s="15" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="E213" s="15" t="s">
-        <v>643</v>
+        <v>661</v>
       </c>
       <c r="F213" s="16" t="n">
         <v>45698</v>
@@ -18776,13 +18896,13 @@
         <v>50</v>
       </c>
       <c r="C214" s="15" t="s">
-        <v>644</v>
+        <v>662</v>
       </c>
       <c r="D214" s="15" t="s">
-        <v>645</v>
+        <v>663</v>
       </c>
       <c r="E214" s="15" t="s">
-        <v>643</v>
+        <v>661</v>
       </c>
       <c r="F214" s="16" t="n">
         <v>45098</v>
@@ -18832,13 +18952,13 @@
         <v>50</v>
       </c>
       <c r="C215" s="15" t="s">
-        <v>646</v>
+        <v>664</v>
       </c>
       <c r="D215" s="15" t="s">
-        <v>645</v>
+        <v>663</v>
       </c>
       <c r="E215" s="15" t="s">
-        <v>643</v>
+        <v>661</v>
       </c>
       <c r="F215" s="16" t="n">
         <v>42849</v>
@@ -18888,13 +19008,13 @@
         <v>50</v>
       </c>
       <c r="C216" s="15" t="s">
-        <v>647</v>
+        <v>665</v>
       </c>
       <c r="D216" s="15" t="s">
-        <v>645</v>
+        <v>663</v>
       </c>
       <c r="E216" s="15" t="s">
-        <v>643</v>
+        <v>661</v>
       </c>
       <c r="F216" s="16" t="n">
         <v>46086</v>
@@ -18944,13 +19064,13 @@
         <v>50</v>
       </c>
       <c r="C217" s="15" t="s">
-        <v>648</v>
+        <v>666</v>
       </c>
       <c r="D217" s="15" t="s">
-        <v>645</v>
+        <v>663</v>
       </c>
       <c r="E217" s="15" t="s">
-        <v>643</v>
+        <v>661</v>
       </c>
       <c r="F217" s="16" t="n">
         <v>45978</v>
@@ -19000,13 +19120,13 @@
         <v>50</v>
       </c>
       <c r="C218" s="15" t="s">
-        <v>649</v>
+        <v>667</v>
       </c>
       <c r="D218" s="15" t="s">
-        <v>645</v>
+        <v>663</v>
       </c>
       <c r="E218" s="15" t="s">
-        <v>643</v>
+        <v>661</v>
       </c>
       <c r="F218" s="16" t="n">
         <v>45936</v>
@@ -19056,13 +19176,13 @@
         <v>50</v>
       </c>
       <c r="C219" s="15" t="s">
-        <v>650</v>
+        <v>668</v>
       </c>
       <c r="D219" s="15" t="s">
-        <v>645</v>
+        <v>663</v>
       </c>
       <c r="E219" s="15" t="s">
-        <v>643</v>
+        <v>661</v>
       </c>
       <c r="F219" s="16" t="n">
         <v>45930</v>
@@ -19112,13 +19232,13 @@
         <v>50</v>
       </c>
       <c r="C220" s="15" t="s">
-        <v>651</v>
+        <v>669</v>
       </c>
       <c r="D220" s="15" t="s">
-        <v>652</v>
+        <v>670</v>
       </c>
       <c r="E220" s="15" t="s">
-        <v>653</v>
+        <v>671</v>
       </c>
       <c r="F220" s="16" t="n">
         <v>45545</v>
@@ -19168,13 +19288,13 @@
         <v>50</v>
       </c>
       <c r="C221" s="15" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="D221" s="15" t="s">
-        <v>652</v>
+        <v>670</v>
       </c>
       <c r="E221" s="15" t="s">
-        <v>653</v>
+        <v>671</v>
       </c>
       <c r="F221" s="16" t="n">
         <v>42919</v>
@@ -19224,13 +19344,13 @@
         <v>50</v>
       </c>
       <c r="C222" s="15" t="s">
-        <v>655</v>
+        <v>673</v>
       </c>
       <c r="D222" s="15" t="s">
-        <v>652</v>
+        <v>670</v>
       </c>
       <c r="E222" s="15" t="s">
-        <v>653</v>
+        <v>671</v>
       </c>
       <c r="F222" s="16" t="n">
         <v>42919</v>
@@ -19280,13 +19400,13 @@
         <v>50</v>
       </c>
       <c r="C223" s="15" t="s">
-        <v>656</v>
+        <v>674</v>
       </c>
       <c r="D223" s="15" t="s">
-        <v>652</v>
+        <v>670</v>
       </c>
       <c r="E223" s="15" t="s">
-        <v>653</v>
+        <v>671</v>
       </c>
       <c r="F223" s="16" t="n">
         <v>45398</v>
@@ -19336,13 +19456,13 @@
         <v>50</v>
       </c>
       <c r="C224" s="15" t="s">
-        <v>657</v>
+        <v>675</v>
       </c>
       <c r="D224" s="15" t="s">
-        <v>652</v>
+        <v>670</v>
       </c>
       <c r="E224" s="15" t="s">
-        <v>653</v>
+        <v>671</v>
       </c>
       <c r="F224" s="16" t="n">
         <v>42919</v>
@@ -19392,13 +19512,13 @@
         <v>50</v>
       </c>
       <c r="C225" s="15" t="s">
-        <v>658</v>
+        <v>676</v>
       </c>
       <c r="D225" s="15" t="s">
-        <v>652</v>
+        <v>670</v>
       </c>
       <c r="E225" s="15" t="s">
-        <v>653</v>
+        <v>671</v>
       </c>
       <c r="F225" s="16" t="n">
         <v>42919</v>
@@ -19448,13 +19568,13 @@
         <v>50</v>
       </c>
       <c r="C226" s="15" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
       <c r="D226" s="15" t="s">
-        <v>652</v>
+        <v>670</v>
       </c>
       <c r="E226" s="15" t="s">
-        <v>653</v>
+        <v>671</v>
       </c>
       <c r="F226" s="16" t="n">
         <v>42919</v>
@@ -19504,13 +19624,13 @@
         <v>50</v>
       </c>
       <c r="C227" s="15" t="s">
-        <v>660</v>
+        <v>678</v>
       </c>
       <c r="D227" s="15" t="s">
-        <v>661</v>
+        <v>679</v>
       </c>
       <c r="E227" s="15" t="s">
-        <v>653</v>
+        <v>671</v>
       </c>
       <c r="F227" s="16" t="n">
         <v>42919</v>
@@ -19560,13 +19680,13 @@
         <v>50</v>
       </c>
       <c r="C228" s="15" t="s">
-        <v>662</v>
+        <v>680</v>
       </c>
       <c r="D228" s="15" t="s">
-        <v>663</v>
+        <v>681</v>
       </c>
       <c r="E228" s="15" t="s">
-        <v>653</v>
+        <v>671</v>
       </c>
       <c r="F228" s="16" t="n">
         <v>45756</v>
@@ -19616,10 +19736,10 @@
         <v>50</v>
       </c>
       <c r="C229" s="15" t="s">
-        <v>664</v>
+        <v>682</v>
       </c>
       <c r="D229" s="15" t="s">
-        <v>665</v>
+        <v>683</v>
       </c>
       <c r="E229" s="15" t="s">
         <v>194</v>
@@ -19672,10 +19792,10 @@
         <v>50</v>
       </c>
       <c r="C230" s="15" t="s">
-        <v>666</v>
+        <v>684</v>
       </c>
       <c r="D230" s="15" t="s">
-        <v>665</v>
+        <v>683</v>
       </c>
       <c r="E230" s="15" t="s">
         <v>194</v>
@@ -19728,10 +19848,10 @@
         <v>50</v>
       </c>
       <c r="C231" s="15" t="s">
-        <v>667</v>
+        <v>685</v>
       </c>
       <c r="D231" s="15" t="s">
-        <v>665</v>
+        <v>683</v>
       </c>
       <c r="E231" s="15" t="s">
         <v>194</v>
@@ -19784,7 +19904,7 @@
         <v>50</v>
       </c>
       <c r="C232" s="15" t="s">
-        <v>668</v>
+        <v>686</v>
       </c>
       <c r="D232" s="15" t="s">
         <v>75</v>
@@ -19840,7 +19960,7 @@
         <v>50</v>
       </c>
       <c r="C233" s="15" t="s">
-        <v>669</v>
+        <v>687</v>
       </c>
       <c r="D233" s="15" t="s">
         <v>75</v>
@@ -19896,7 +20016,7 @@
         <v>50</v>
       </c>
       <c r="C234" s="15" t="s">
-        <v>670</v>
+        <v>688</v>
       </c>
       <c r="D234" s="15" t="s">
         <v>75</v>
@@ -19952,7 +20072,7 @@
         <v>50</v>
       </c>
       <c r="C235" s="15" t="s">
-        <v>671</v>
+        <v>689</v>
       </c>
       <c r="D235" s="15" t="s">
         <v>75</v>
@@ -20008,7 +20128,7 @@
         <v>50</v>
       </c>
       <c r="C236" s="15" t="s">
-        <v>672</v>
+        <v>690</v>
       </c>
       <c r="D236" s="15" t="s">
         <v>75</v>
@@ -20064,7 +20184,7 @@
         <v>50</v>
       </c>
       <c r="C237" s="15" t="s">
-        <v>673</v>
+        <v>691</v>
       </c>
       <c r="D237" s="15" t="s">
         <v>75</v>
@@ -20120,10 +20240,10 @@
         <v>50</v>
       </c>
       <c r="C238" s="15" t="s">
-        <v>674</v>
+        <v>692</v>
       </c>
       <c r="D238" s="15" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="E238" s="15" t="s">
         <v>194</v>
@@ -20176,10 +20296,10 @@
         <v>50</v>
       </c>
       <c r="C239" s="15" t="s">
-        <v>675</v>
+        <v>693</v>
       </c>
       <c r="D239" s="15" t="s">
-        <v>676</v>
+        <v>694</v>
       </c>
       <c r="E239" s="15" t="s">
         <v>194</v>
@@ -20232,10 +20352,10 @@
         <v>50</v>
       </c>
       <c r="C240" s="15" t="s">
-        <v>677</v>
+        <v>695</v>
       </c>
       <c r="D240" s="15" t="s">
-        <v>676</v>
+        <v>694</v>
       </c>
       <c r="E240" s="15" t="s">
         <v>194</v>
@@ -20288,10 +20408,10 @@
         <v>50</v>
       </c>
       <c r="C241" s="15" t="s">
-        <v>678</v>
+        <v>696</v>
       </c>
       <c r="D241" s="15" t="s">
-        <v>676</v>
+        <v>694</v>
       </c>
       <c r="E241" s="15" t="s">
         <v>194</v>
@@ -20344,10 +20464,10 @@
         <v>50</v>
       </c>
       <c r="C242" s="15" t="s">
-        <v>679</v>
+        <v>697</v>
       </c>
       <c r="D242" s="15" t="s">
-        <v>676</v>
+        <v>694</v>
       </c>
       <c r="E242" s="15" t="s">
         <v>194</v>
@@ -20400,10 +20520,10 @@
         <v>50</v>
       </c>
       <c r="C243" s="15" t="s">
-        <v>680</v>
+        <v>698</v>
       </c>
       <c r="D243" s="15" t="s">
-        <v>676</v>
+        <v>694</v>
       </c>
       <c r="E243" s="15" t="s">
         <v>194</v>
@@ -20456,10 +20576,10 @@
         <v>50</v>
       </c>
       <c r="C244" s="15" t="s">
-        <v>681</v>
+        <v>699</v>
       </c>
       <c r="D244" s="15" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="E244" s="15" t="s">
         <v>194</v>
@@ -20512,10 +20632,10 @@
         <v>50</v>
       </c>
       <c r="C245" s="15" t="s">
-        <v>682</v>
+        <v>700</v>
       </c>
       <c r="D245" s="15" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="E245" s="15" t="s">
         <v>194</v>
@@ -20568,13 +20688,13 @@
         <v>50</v>
       </c>
       <c r="C246" s="15" t="s">
-        <v>683</v>
+        <v>701</v>
       </c>
       <c r="D246" s="15" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="E246" s="15" t="s">
-        <v>684</v>
+        <v>702</v>
       </c>
       <c r="F246" s="16" t="n">
         <v>43024</v>
@@ -20624,13 +20744,13 @@
         <v>50</v>
       </c>
       <c r="C247" s="15" t="s">
-        <v>685</v>
+        <v>703</v>
       </c>
       <c r="D247" s="15" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="E247" s="15" t="s">
-        <v>684</v>
+        <v>702</v>
       </c>
       <c r="F247" s="16" t="n">
         <v>41219</v>
@@ -20680,13 +20800,13 @@
         <v>50</v>
       </c>
       <c r="C248" s="15" t="s">
-        <v>686</v>
+        <v>704</v>
       </c>
       <c r="D248" s="15" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="E248" s="15" t="s">
-        <v>684</v>
+        <v>702</v>
       </c>
       <c r="F248" s="16" t="n">
         <v>43557</v>
@@ -20736,13 +20856,13 @@
         <v>50</v>
       </c>
       <c r="C249" s="15" t="s">
-        <v>687</v>
+        <v>705</v>
       </c>
       <c r="D249" s="15" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="E249" s="15" t="s">
-        <v>684</v>
+        <v>702</v>
       </c>
       <c r="F249" s="16" t="n">
         <v>41183</v>
@@ -20792,13 +20912,13 @@
         <v>50</v>
       </c>
       <c r="C250" s="15" t="s">
-        <v>688</v>
+        <v>706</v>
       </c>
       <c r="D250" s="15" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="E250" s="15" t="s">
-        <v>684</v>
+        <v>702</v>
       </c>
       <c r="F250" s="16" t="n">
         <v>40035</v>
@@ -20848,13 +20968,13 @@
         <v>50</v>
       </c>
       <c r="C251" s="15" t="s">
-        <v>689</v>
+        <v>707</v>
       </c>
       <c r="D251" s="15" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="E251" s="15" t="s">
-        <v>684</v>
+        <v>702</v>
       </c>
       <c r="F251" s="16" t="n">
         <v>44879</v>
@@ -20904,13 +21024,13 @@
         <v>50</v>
       </c>
       <c r="C252" s="15" t="s">
-        <v>690</v>
+        <v>708</v>
       </c>
       <c r="D252" s="15" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="E252" s="15" t="s">
-        <v>684</v>
+        <v>702</v>
       </c>
       <c r="F252" s="16" t="n">
         <v>41375</v>
@@ -20960,13 +21080,13 @@
         <v>50</v>
       </c>
       <c r="C253" s="15" t="s">
-        <v>691</v>
+        <v>709</v>
       </c>
       <c r="D253" s="15" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="E253" s="15" t="s">
-        <v>684</v>
+        <v>702</v>
       </c>
       <c r="F253" s="16" t="n">
         <v>43557</v>
@@ -21016,13 +21136,13 @@
         <v>50</v>
       </c>
       <c r="C254" s="15" t="s">
-        <v>692</v>
+        <v>710</v>
       </c>
       <c r="D254" s="15" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="E254" s="15" t="s">
-        <v>684</v>
+        <v>702</v>
       </c>
       <c r="F254" s="16" t="n">
         <v>39875</v>
@@ -21069,16 +21189,16 @@
         <v>254</v>
       </c>
       <c r="B255" s="12" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C255" s="15" t="s">
-        <v>693</v>
+        <v>711</v>
       </c>
       <c r="D255" s="15" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="E255" s="15" t="s">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="F255" s="16" t="n">
         <v>45722</v>
@@ -21127,16 +21247,16 @@
         <v>255</v>
       </c>
       <c r="B256" s="12" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C256" s="15" t="s">
-        <v>695</v>
+        <v>713</v>
       </c>
       <c r="D256" s="15" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="E256" s="15" t="s">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="F256" s="16" t="n">
         <v>45797</v>
@@ -21183,16 +21303,16 @@
         <v>256</v>
       </c>
       <c r="B257" s="12" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C257" s="15" t="s">
-        <v>696</v>
+        <v>714</v>
       </c>
       <c r="D257" s="15" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="E257" s="15" t="s">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="F257" s="16" t="n">
         <v>46083</v>
@@ -21241,16 +21361,16 @@
         <v>257</v>
       </c>
       <c r="B258" s="12" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C258" s="15" t="s">
-        <v>697</v>
+        <v>715</v>
       </c>
       <c r="D258" s="15" t="s">
         <v>75</v>
       </c>
       <c r="E258" s="15" t="s">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="F258" s="16" t="n">
         <v>46091</v>
@@ -21297,16 +21417,16 @@
         <v>258</v>
       </c>
       <c r="B259" s="12" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C259" s="15" t="s">
-        <v>698</v>
+        <v>716</v>
       </c>
       <c r="D259" s="15" t="s">
         <v>75</v>
       </c>
       <c r="E259" s="15" t="s">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="F259" s="16" t="n">
         <v>45867</v>
@@ -21353,16 +21473,16 @@
         <v>259</v>
       </c>
       <c r="B260" s="12" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C260" s="15" t="s">
-        <v>699</v>
+        <v>717</v>
       </c>
       <c r="D260" s="15" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="E260" s="15" t="s">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="F260" s="16" t="n">
         <v>45497</v>
@@ -21409,16 +21529,16 @@
         <v>260</v>
       </c>
       <c r="B261" s="12" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C261" s="15" t="s">
-        <v>700</v>
+        <v>718</v>
       </c>
       <c r="D261" s="15" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="E261" s="15" t="s">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="F261" s="16" t="n">
         <v>46181</v>
@@ -21467,16 +21587,16 @@
         <v>261</v>
       </c>
       <c r="B262" s="12" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C262" s="15" t="s">
-        <v>701</v>
+        <v>719</v>
       </c>
       <c r="D262" s="15" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="E262" s="15" t="s">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="F262" s="16" t="n">
         <v>45968</v>
@@ -21507,7 +21627,7 @@
       </c>
       <c r="N262" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H262,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O262" s="17"/>
       <c r="P262" s="16" t="str">
@@ -21525,16 +21645,16 @@
         <v>262</v>
       </c>
       <c r="B263" s="12" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C263" s="15" t="s">
-        <v>702</v>
+        <v>720</v>
       </c>
       <c r="D263" s="15" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E263" s="15" t="s">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="F263" s="16" t="n">
         <v>45509</v>
@@ -21565,7 +21685,7 @@
       </c>
       <c r="N263" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H263,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O263" s="17"/>
       <c r="P263" s="16" t="str">
@@ -21583,16 +21703,16 @@
         <v>263</v>
       </c>
       <c r="B264" s="12" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C264" s="15" t="s">
-        <v>703</v>
+        <v>721</v>
       </c>
       <c r="D264" s="15" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E264" s="15" t="s">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="F264" s="16" t="n">
         <v>45506</v>
@@ -21623,7 +21743,7 @@
       </c>
       <c r="N264" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H264,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O264" s="17"/>
       <c r="P264" s="16" t="str">
@@ -21641,16 +21761,16 @@
         <v>264</v>
       </c>
       <c r="B265" s="12" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C265" s="15" t="s">
-        <v>704</v>
+        <v>722</v>
       </c>
       <c r="D265" s="15" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="E265" s="15" t="s">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="F265" s="16" t="n">
         <v>39730</v>
@@ -21697,16 +21817,16 @@
         <v>265</v>
       </c>
       <c r="B266" s="12" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C266" s="15" t="s">
-        <v>705</v>
+        <v>723</v>
       </c>
       <c r="D266" s="15" t="s">
-        <v>706</v>
+        <v>724</v>
       </c>
       <c r="E266" s="15" t="s">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="F266" s="16" t="n">
         <v>45853</v>
@@ -21735,7 +21855,7 @@
       </c>
       <c r="N266" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H266,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O266" s="17"/>
       <c r="P266" s="16" t="str">
@@ -21753,16 +21873,16 @@
         <v>266</v>
       </c>
       <c r="B267" s="12" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C267" s="15" t="s">
-        <v>707</v>
+        <v>725</v>
       </c>
       <c r="D267" s="15" t="s">
         <v>79</v>
       </c>
       <c r="E267" s="15" t="s">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="F267" s="16" t="n">
         <v>46125</v>
@@ -21791,7 +21911,7 @@
       </c>
       <c r="N267" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H267,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O267" s="17"/>
       <c r="P267" s="16" t="str">
@@ -21809,16 +21929,16 @@
         <v>267</v>
       </c>
       <c r="B268" s="12" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C268" s="15" t="s">
-        <v>708</v>
+        <v>726</v>
       </c>
       <c r="D268" s="15" t="s">
         <v>79</v>
       </c>
       <c r="E268" s="15" t="s">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="F268" s="16" t="n">
         <v>45968</v>
@@ -21849,7 +21969,7 @@
       </c>
       <c r="N268" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H268,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O268" s="17"/>
       <c r="P268" s="16" t="str">
@@ -21867,16 +21987,16 @@
         <v>268</v>
       </c>
       <c r="B269" s="12" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C269" s="15" t="s">
-        <v>709</v>
+        <v>727</v>
       </c>
       <c r="D269" s="15" t="s">
-        <v>710</v>
+        <v>728</v>
       </c>
       <c r="E269" s="15" t="s">
-        <v>694</v>
+        <v>712</v>
       </c>
       <c r="F269" s="16" t="n">
         <v>45460</v>
@@ -21925,16 +22045,16 @@
         <v>269</v>
       </c>
       <c r="B270" s="12" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C270" s="15" t="s">
-        <v>711</v>
+        <v>729</v>
       </c>
       <c r="D270" s="15" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="E270" s="15" t="s">
-        <v>712</v>
+        <v>730</v>
       </c>
       <c r="F270" s="16" t="n">
         <v>45817</v>
@@ -21981,16 +22101,16 @@
         <v>270</v>
       </c>
       <c r="B271" s="12" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C271" s="15" t="s">
-        <v>713</v>
+        <v>731</v>
       </c>
       <c r="D271" s="15" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="E271" s="15" t="s">
-        <v>714</v>
+        <v>732</v>
       </c>
       <c r="F271" s="16" t="n">
         <v>45967</v>
@@ -22039,16 +22159,16 @@
         <v>271</v>
       </c>
       <c r="B272" s="12" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C272" s="15" t="s">
-        <v>715</v>
+        <v>733</v>
       </c>
       <c r="D272" s="15" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="E272" s="15" t="s">
-        <v>714</v>
+        <v>732</v>
       </c>
       <c r="F272" s="16" t="n">
         <v>45999</v>
@@ -22097,16 +22217,16 @@
         <v>272</v>
       </c>
       <c r="B273" s="12" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C273" s="15" t="s">
-        <v>716</v>
+        <v>734</v>
       </c>
       <c r="D273" s="15" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="E273" s="15" t="s">
-        <v>714</v>
+        <v>732</v>
       </c>
       <c r="F273" s="16" t="n">
         <v>45882</v>
@@ -22155,16 +22275,16 @@
         <v>273</v>
       </c>
       <c r="B274" s="12" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C274" s="15" t="s">
-        <v>717</v>
+        <v>735</v>
       </c>
       <c r="D274" s="15" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="E274" s="15" t="s">
-        <v>714</v>
+        <v>732</v>
       </c>
       <c r="F274" s="16" t="n">
         <v>45847</v>
@@ -22213,16 +22333,16 @@
         <v>274</v>
       </c>
       <c r="B275" s="12" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C275" s="15" t="s">
-        <v>718</v>
+        <v>736</v>
       </c>
       <c r="D275" s="15" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="E275" s="15" t="s">
-        <v>714</v>
+        <v>732</v>
       </c>
       <c r="F275" s="16" t="n">
         <v>45908</v>
@@ -22269,16 +22389,16 @@
         <v>275</v>
       </c>
       <c r="B276" s="12" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C276" s="15" t="s">
-        <v>719</v>
+        <v>737</v>
       </c>
       <c r="D276" s="15" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="E276" s="15" t="s">
-        <v>714</v>
+        <v>732</v>
       </c>
       <c r="F276" s="16" t="n">
         <v>46007</v>
@@ -22327,16 +22447,16 @@
         <v>276</v>
       </c>
       <c r="B277" s="12" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C277" s="15" t="s">
-        <v>720</v>
+        <v>738</v>
       </c>
       <c r="D277" s="15" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="E277" s="15" t="s">
-        <v>714</v>
+        <v>732</v>
       </c>
       <c r="F277" s="16" t="n">
         <v>45958</v>
@@ -22383,16 +22503,16 @@
         <v>277</v>
       </c>
       <c r="B278" s="12" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C278" s="15" t="s">
-        <v>721</v>
+        <v>739</v>
       </c>
       <c r="D278" s="15" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="E278" s="15" t="s">
-        <v>714</v>
+        <v>732</v>
       </c>
       <c r="F278" s="16" t="n">
         <v>46056</v>
@@ -22441,16 +22561,16 @@
         <v>278</v>
       </c>
       <c r="B279" s="12" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C279" s="15" t="s">
-        <v>722</v>
+        <v>740</v>
       </c>
       <c r="D279" s="15" t="s">
-        <v>723</v>
+        <v>741</v>
       </c>
       <c r="E279" s="15" t="s">
-        <v>714</v>
+        <v>732</v>
       </c>
       <c r="F279" s="16" t="n">
         <v>45966</v>
@@ -22497,16 +22617,16 @@
         <v>279</v>
       </c>
       <c r="B280" s="12" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C280" s="15" t="s">
-        <v>724</v>
+        <v>742</v>
       </c>
       <c r="D280" s="15" t="s">
-        <v>723</v>
+        <v>741</v>
       </c>
       <c r="E280" s="15" t="s">
-        <v>714</v>
+        <v>732</v>
       </c>
       <c r="F280" s="16" t="n">
         <v>46055</v>
@@ -22555,16 +22675,16 @@
         <v>280</v>
       </c>
       <c r="B281" s="12" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C281" s="15" t="s">
-        <v>725</v>
+        <v>743</v>
       </c>
       <c r="D281" s="15" t="s">
-        <v>723</v>
+        <v>741</v>
       </c>
       <c r="E281" s="15" t="s">
-        <v>714</v>
+        <v>732</v>
       </c>
       <c r="F281" s="16" t="n">
         <v>45932</v>
@@ -22611,16 +22731,16 @@
         <v>281</v>
       </c>
       <c r="B282" s="12" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C282" s="15" t="s">
-        <v>726</v>
+        <v>744</v>
       </c>
       <c r="D282" s="15" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="E282" s="15" t="s">
-        <v>727</v>
+        <v>745</v>
       </c>
       <c r="F282" s="16" t="n">
         <v>45918</v>
@@ -22649,7 +22769,7 @@
       </c>
       <c r="N282" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H282,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O282" s="17"/>
       <c r="P282" s="16" t="str">
@@ -22667,16 +22787,16 @@
         <v>282</v>
       </c>
       <c r="B283" s="12" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C283" s="15" t="s">
-        <v>728</v>
+        <v>746</v>
       </c>
       <c r="D283" s="15" t="s">
         <v>79</v>
       </c>
       <c r="E283" s="15" t="s">
-        <v>727</v>
+        <v>745</v>
       </c>
       <c r="F283" s="16" t="n">
         <v>45845</v>
@@ -22705,7 +22825,7 @@
       </c>
       <c r="N283" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H283,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O283" s="17"/>
       <c r="P283" s="16" t="str">
@@ -22723,16 +22843,16 @@
         <v>283</v>
       </c>
       <c r="B284" s="12" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C284" s="15" t="s">
-        <v>729</v>
+        <v>747</v>
       </c>
       <c r="D284" s="15" t="s">
         <v>79</v>
       </c>
       <c r="E284" s="15" t="s">
-        <v>727</v>
+        <v>745</v>
       </c>
       <c r="F284" s="16" t="n">
         <v>45875</v>
@@ -22763,7 +22883,7 @@
       </c>
       <c r="N284" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H284,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O284" s="17"/>
       <c r="P284" s="16" t="str">
@@ -22781,16 +22901,16 @@
         <v>284</v>
       </c>
       <c r="B285" s="12" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C285" s="15" t="s">
-        <v>730</v>
+        <v>748</v>
       </c>
       <c r="D285" s="15" t="s">
         <v>79</v>
       </c>
       <c r="E285" s="15" t="s">
-        <v>727</v>
+        <v>745</v>
       </c>
       <c r="F285" s="16" t="n">
         <v>45838</v>
@@ -22821,7 +22941,7 @@
       </c>
       <c r="N285" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H285,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O285" s="17"/>
       <c r="P285" s="16" t="str">
@@ -22839,16 +22959,16 @@
         <v>285</v>
       </c>
       <c r="B286" s="12" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C286" s="15" t="s">
-        <v>731</v>
+        <v>749</v>
       </c>
       <c r="D286" s="15" t="s">
         <v>79</v>
       </c>
       <c r="E286" s="15" t="s">
-        <v>727</v>
+        <v>745</v>
       </c>
       <c r="F286" s="16" t="n">
         <v>45992</v>
@@ -22879,7 +22999,7 @@
       </c>
       <c r="N286" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H286,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O286" s="17"/>
       <c r="P286" s="16" t="str">
@@ -22897,16 +23017,16 @@
         <v>286</v>
       </c>
       <c r="B287" s="12" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C287" s="15" t="s">
-        <v>732</v>
+        <v>750</v>
       </c>
       <c r="D287" s="15" t="s">
         <v>75</v>
       </c>
       <c r="E287" s="15" t="s">
-        <v>733</v>
+        <v>751</v>
       </c>
       <c r="F287" s="16" t="n">
         <v>45989</v>
@@ -22955,16 +23075,16 @@
         <v>287</v>
       </c>
       <c r="B288" s="12" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C288" s="15" t="s">
-        <v>734</v>
+        <v>752</v>
       </c>
       <c r="D288" s="15" t="s">
-        <v>735</v>
+        <v>753</v>
       </c>
       <c r="E288" s="15" t="s">
-        <v>736</v>
+        <v>754</v>
       </c>
       <c r="F288" s="16" t="n">
         <v>46223</v>
@@ -23013,16 +23133,16 @@
         <v>288</v>
       </c>
       <c r="B289" s="12" t="s">
-        <v>737</v>
+        <v>755</v>
       </c>
       <c r="C289" s="15" t="s">
-        <v>738</v>
+        <v>756</v>
       </c>
       <c r="D289" s="15" t="s">
-        <v>735</v>
+        <v>753</v>
       </c>
       <c r="E289" s="15" t="s">
-        <v>739</v>
+        <v>757</v>
       </c>
       <c r="F289" s="16" t="n">
         <v>46002</v>
@@ -23072,13 +23192,13 @@
         <v>72</v>
       </c>
       <c r="C290" s="15" t="s">
-        <v>740</v>
+        <v>758</v>
       </c>
       <c r="D290" s="15" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="E290" s="15" t="s">
-        <v>741</v>
+        <v>759</v>
       </c>
       <c r="F290" s="16" t="n">
         <v>46191</v>
@@ -23130,13 +23250,13 @@
         <v>72</v>
       </c>
       <c r="C291" s="15" t="s">
-        <v>742</v>
+        <v>760</v>
       </c>
       <c r="D291" s="15" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="E291" s="15" t="s">
-        <v>741</v>
+        <v>759</v>
       </c>
       <c r="F291" s="16" t="n">
         <v>46245</v>
@@ -23186,13 +23306,13 @@
         <v>72</v>
       </c>
       <c r="C292" s="15" t="s">
-        <v>743</v>
+        <v>761</v>
       </c>
       <c r="D292" s="15" t="s">
-        <v>645</v>
+        <v>663</v>
       </c>
       <c r="E292" s="15" t="s">
-        <v>741</v>
+        <v>759</v>
       </c>
       <c r="F292" s="16" t="n">
         <v>45944</v>
@@ -23242,13 +23362,13 @@
         <v>72</v>
       </c>
       <c r="C293" s="15" t="s">
-        <v>744</v>
+        <v>762</v>
       </c>
       <c r="D293" s="15" t="s">
-        <v>645</v>
+        <v>663</v>
       </c>
       <c r="E293" s="15" t="s">
-        <v>741</v>
+        <v>759</v>
       </c>
       <c r="F293" s="16" t="n">
         <v>46261</v>
@@ -23300,13 +23420,13 @@
         <v>72</v>
       </c>
       <c r="C294" s="15" t="s">
-        <v>745</v>
+        <v>763</v>
       </c>
       <c r="D294" s="15" t="s">
-        <v>645</v>
+        <v>663</v>
       </c>
       <c r="E294" s="15" t="s">
-        <v>741</v>
+        <v>759</v>
       </c>
       <c r="F294" s="16" t="n">
         <v>46104</v>
@@ -23356,13 +23476,13 @@
         <v>72</v>
       </c>
       <c r="C295" s="15" t="s">
-        <v>746</v>
+        <v>764</v>
       </c>
       <c r="D295" s="15" t="s">
-        <v>645</v>
+        <v>663</v>
       </c>
       <c r="E295" s="15" t="s">
-        <v>741</v>
+        <v>759</v>
       </c>
       <c r="F295" s="16" t="n">
         <v>46113</v>
@@ -23412,13 +23532,13 @@
         <v>72</v>
       </c>
       <c r="C296" s="15" t="s">
-        <v>747</v>
+        <v>765</v>
       </c>
       <c r="D296" s="15" t="s">
-        <v>748</v>
+        <v>766</v>
       </c>
       <c r="E296" s="15" t="s">
-        <v>741</v>
+        <v>759</v>
       </c>
       <c r="F296" s="16" t="n">
         <v>45446</v>
@@ -23468,10 +23588,10 @@
         <v>72</v>
       </c>
       <c r="C297" s="15" t="s">
-        <v>749</v>
+        <v>767</v>
       </c>
       <c r="D297" s="15" t="s">
-        <v>633</v>
+        <v>651</v>
       </c>
       <c r="E297" s="15" t="s">
         <v>71</v>
@@ -23524,10 +23644,10 @@
         <v>72</v>
       </c>
       <c r="C298" s="15" t="s">
-        <v>750</v>
+        <v>768</v>
       </c>
       <c r="D298" s="15" t="s">
-        <v>751</v>
+        <v>769</v>
       </c>
       <c r="E298" s="15" t="s">
         <v>71</v>
@@ -23580,13 +23700,13 @@
         <v>72</v>
       </c>
       <c r="C299" s="15" t="s">
-        <v>752</v>
+        <v>770</v>
       </c>
       <c r="D299" s="15" t="s">
         <v>99</v>
       </c>
       <c r="E299" s="15" t="s">
-        <v>753</v>
+        <v>771</v>
       </c>
       <c r="F299" s="16" t="n">
         <v>46148</v>
@@ -23636,13 +23756,13 @@
         <v>72</v>
       </c>
       <c r="C300" s="15" t="s">
-        <v>754</v>
+        <v>772</v>
       </c>
       <c r="D300" s="15" t="s">
         <v>99</v>
       </c>
       <c r="E300" s="15" t="s">
-        <v>753</v>
+        <v>771</v>
       </c>
       <c r="F300" s="16" t="n">
         <v>46195</v>
@@ -23694,13 +23814,13 @@
         <v>72</v>
       </c>
       <c r="C301" s="15" t="s">
-        <v>755</v>
+        <v>773</v>
       </c>
       <c r="D301" s="15" t="s">
         <v>99</v>
       </c>
       <c r="E301" s="15" t="s">
-        <v>753</v>
+        <v>771</v>
       </c>
       <c r="F301" s="16" t="n">
         <v>46034</v>
@@ -23750,13 +23870,13 @@
         <v>72</v>
       </c>
       <c r="C302" s="15" t="s">
-        <v>756</v>
+        <v>774</v>
       </c>
       <c r="D302" s="15" t="s">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="E302" s="15" t="s">
-        <v>753</v>
+        <v>771</v>
       </c>
       <c r="F302" s="16" t="n">
         <v>45924</v>
@@ -23808,13 +23928,13 @@
         <v>72</v>
       </c>
       <c r="C303" s="15" t="s">
-        <v>757</v>
+        <v>775</v>
       </c>
       <c r="D303" s="15" t="s">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="E303" s="15" t="s">
-        <v>753</v>
+        <v>771</v>
       </c>
       <c r="F303" s="16" t="n">
         <v>45922</v>
@@ -23866,13 +23986,13 @@
         <v>72</v>
       </c>
       <c r="C304" s="15" t="s">
-        <v>758</v>
+        <v>776</v>
       </c>
       <c r="D304" s="15" t="s">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="E304" s="15" t="s">
-        <v>753</v>
+        <v>771</v>
       </c>
       <c r="F304" s="16" t="n">
         <v>46044</v>
@@ -23922,13 +24042,13 @@
         <v>72</v>
       </c>
       <c r="C305" s="15" t="s">
-        <v>759</v>
+        <v>777</v>
       </c>
       <c r="D305" s="15" t="s">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="E305" s="15" t="s">
-        <v>753</v>
+        <v>771</v>
       </c>
       <c r="F305" s="16" t="n">
         <v>45993</v>
@@ -23978,13 +24098,13 @@
         <v>72</v>
       </c>
       <c r="C306" s="15" t="s">
-        <v>760</v>
+        <v>778</v>
       </c>
       <c r="D306" s="15" t="s">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="E306" s="15" t="s">
-        <v>753</v>
+        <v>771</v>
       </c>
       <c r="F306" s="16" t="n">
         <v>46001</v>
@@ -24034,13 +24154,13 @@
         <v>72</v>
       </c>
       <c r="C307" s="15" t="s">
-        <v>761</v>
+        <v>779</v>
       </c>
       <c r="D307" s="15" t="s">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="E307" s="15" t="s">
-        <v>753</v>
+        <v>771</v>
       </c>
       <c r="F307" s="16" t="n">
         <v>45993</v>
@@ -24090,13 +24210,13 @@
         <v>72</v>
       </c>
       <c r="C308" s="15" t="s">
-        <v>762</v>
+        <v>780</v>
       </c>
       <c r="D308" s="15" t="s">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="E308" s="15" t="s">
-        <v>763</v>
+        <v>781</v>
       </c>
       <c r="F308" s="16" t="n">
         <v>46119</v>
@@ -24137,7 +24257,7 @@
         <v/>
       </c>
       <c r="R308" s="9" t="s">
-        <v>764</v>
+        <v>782</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24148,13 +24268,13 @@
         <v>72</v>
       </c>
       <c r="C309" s="15" t="s">
-        <v>765</v>
+        <v>783</v>
       </c>
       <c r="D309" s="15" t="s">
-        <v>561</v>
+        <v>579</v>
       </c>
       <c r="E309" s="15" t="s">
-        <v>763</v>
+        <v>781</v>
       </c>
       <c r="F309" s="16" t="n">
         <v>46094</v>
@@ -24195,7 +24315,7 @@
         <v/>
       </c>
       <c r="R309" s="9" t="s">
-        <v>764</v>
+        <v>782</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24206,13 +24326,13 @@
         <v>72</v>
       </c>
       <c r="C310" s="15" t="s">
-        <v>766</v>
+        <v>784</v>
       </c>
       <c r="D310" s="15" t="s">
-        <v>767</v>
+        <v>785</v>
       </c>
       <c r="E310" s="15" t="s">
-        <v>753</v>
+        <v>771</v>
       </c>
       <c r="F310" s="16" t="n">
         <v>45798</v>
@@ -24262,13 +24382,13 @@
         <v>72</v>
       </c>
       <c r="C311" s="15" t="s">
-        <v>768</v>
+        <v>786</v>
       </c>
       <c r="D311" s="15" t="s">
-        <v>767</v>
+        <v>785</v>
       </c>
       <c r="E311" s="15" t="s">
-        <v>753</v>
+        <v>771</v>
       </c>
       <c r="F311" s="16" t="n">
         <v>45744</v>
@@ -24318,13 +24438,13 @@
         <v>72</v>
       </c>
       <c r="C312" s="15" t="s">
-        <v>769</v>
+        <v>787</v>
       </c>
       <c r="D312" s="15" t="s">
-        <v>770</v>
+        <v>788</v>
       </c>
       <c r="E312" s="15" t="s">
-        <v>753</v>
+        <v>771</v>
       </c>
       <c r="F312" s="16" t="n">
         <v>45812</v>
@@ -24374,13 +24494,13 @@
         <v>50</v>
       </c>
       <c r="C313" s="15" t="s">
+        <v>789</v>
+      </c>
+      <c r="D313" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="E313" s="15" t="s">
         <v>771</v>
-      </c>
-      <c r="D313" s="15" t="s">
-        <v>335</v>
-      </c>
-      <c r="E313" s="15" t="s">
-        <v>753</v>
       </c>
       <c r="F313" s="16" t="n">
         <v>45938</v>
@@ -24430,13 +24550,13 @@
         <v>72</v>
       </c>
       <c r="C314" s="15" t="s">
-        <v>772</v>
+        <v>790</v>
       </c>
       <c r="D314" s="15" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="E314" s="15" t="s">
-        <v>753</v>
+        <v>771</v>
       </c>
       <c r="F314" s="16" t="n">
         <v>45910</v>
@@ -24486,13 +24606,13 @@
         <v>72</v>
       </c>
       <c r="C315" s="15" t="s">
-        <v>773</v>
+        <v>791</v>
       </c>
       <c r="D315" s="15" t="s">
-        <v>774</v>
+        <v>792</v>
       </c>
       <c r="E315" s="15" t="s">
-        <v>753</v>
+        <v>771</v>
       </c>
       <c r="F315" s="16" t="n">
         <v>46084</v>
@@ -24545,10 +24665,10 @@
         <v>172</v>
       </c>
       <c r="D316" s="15" t="s">
-        <v>561</v>
+        <v>579</v>
       </c>
       <c r="E316" s="15" t="s">
-        <v>753</v>
+        <v>771</v>
       </c>
       <c r="F316" s="16" t="n">
         <v>45931</v>
@@ -24605,10 +24725,10 @@
         <v>174</v>
       </c>
       <c r="D317" s="15" t="s">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="E317" s="15" t="s">
-        <v>753</v>
+        <v>771</v>
       </c>
       <c r="F317" s="16" t="n">
         <v>45932</v>
@@ -24662,10 +24782,10 @@
         <v>72</v>
       </c>
       <c r="C318" s="15" t="s">
-        <v>775</v>
+        <v>793</v>
       </c>
       <c r="D318" s="15" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="E318" s="15" t="s">
         <v>204</v>
@@ -24718,10 +24838,10 @@
         <v>72</v>
       </c>
       <c r="C319" s="15" t="s">
-        <v>776</v>
+        <v>794</v>
       </c>
       <c r="D319" s="15" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="E319" s="15" t="s">
         <v>204</v>
@@ -24774,10 +24894,10 @@
         <v>72</v>
       </c>
       <c r="C320" s="15" t="s">
-        <v>777</v>
+        <v>795</v>
       </c>
       <c r="D320" s="15" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="E320" s="15" t="s">
         <v>204</v>
@@ -24832,10 +24952,10 @@
         <v>72</v>
       </c>
       <c r="C321" s="15" t="s">
-        <v>778</v>
+        <v>796</v>
       </c>
       <c r="D321" s="15" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="E321" s="15" t="s">
         <v>204</v>
@@ -24890,10 +25010,10 @@
         <v>72</v>
       </c>
       <c r="C322" s="15" t="s">
-        <v>779</v>
+        <v>797</v>
       </c>
       <c r="D322" s="15" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="E322" s="15" t="s">
         <v>204</v>
@@ -24946,7 +25066,7 @@
         <v>72</v>
       </c>
       <c r="C323" s="15" t="s">
-        <v>780</v>
+        <v>798</v>
       </c>
       <c r="D323" s="15" t="s">
         <v>84</v>
@@ -25002,7 +25122,7 @@
         <v>72</v>
       </c>
       <c r="C324" s="15" t="s">
-        <v>781</v>
+        <v>799</v>
       </c>
       <c r="D324" s="15" t="s">
         <v>84</v>
@@ -25058,10 +25178,10 @@
         <v>72</v>
       </c>
       <c r="C325" s="15" t="s">
-        <v>782</v>
+        <v>800</v>
       </c>
       <c r="D325" s="15" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E325" s="15" t="s">
         <v>204</v>
@@ -25114,10 +25234,10 @@
         <v>72</v>
       </c>
       <c r="C326" s="15" t="s">
-        <v>783</v>
+        <v>801</v>
       </c>
       <c r="D326" s="15" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E326" s="15" t="s">
         <v>204</v>
@@ -25170,10 +25290,10 @@
         <v>72</v>
       </c>
       <c r="C327" s="15" t="s">
-        <v>784</v>
+        <v>802</v>
       </c>
       <c r="D327" s="15" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E327" s="15" t="s">
         <v>204</v>
@@ -25226,10 +25346,10 @@
         <v>72</v>
       </c>
       <c r="C328" s="15" t="s">
-        <v>785</v>
+        <v>803</v>
       </c>
       <c r="D328" s="15" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="E328" s="15" t="s">
         <v>204</v>
@@ -25282,13 +25402,13 @@
         <v>72</v>
       </c>
       <c r="C329" s="15" t="s">
-        <v>786</v>
+        <v>804</v>
       </c>
       <c r="D329" s="15" t="s">
-        <v>787</v>
+        <v>805</v>
       </c>
       <c r="E329" s="15" t="s">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="F329" s="16" t="n">
         <v>44718</v>
@@ -25338,13 +25458,13 @@
         <v>72</v>
       </c>
       <c r="C330" s="15" t="s">
-        <v>789</v>
+        <v>807</v>
       </c>
       <c r="D330" s="15" t="s">
-        <v>787</v>
+        <v>805</v>
       </c>
       <c r="E330" s="15" t="s">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="F330" s="16" t="n">
         <v>45194</v>
@@ -25394,13 +25514,13 @@
         <v>72</v>
       </c>
       <c r="C331" s="15" t="s">
-        <v>790</v>
+        <v>808</v>
       </c>
       <c r="D331" s="15" t="s">
-        <v>787</v>
+        <v>805</v>
       </c>
       <c r="E331" s="15" t="s">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="F331" s="16" t="n">
         <v>44621</v>
@@ -25450,13 +25570,13 @@
         <v>72</v>
       </c>
       <c r="C332" s="15" t="s">
-        <v>791</v>
+        <v>809</v>
       </c>
       <c r="D332" s="15" t="s">
-        <v>787</v>
+        <v>805</v>
       </c>
       <c r="E332" s="15" t="s">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="F332" s="16" t="n">
         <v>43132</v>
@@ -25506,13 +25626,13 @@
         <v>72</v>
       </c>
       <c r="C333" s="15" t="s">
-        <v>792</v>
+        <v>810</v>
       </c>
       <c r="D333" s="15" t="s">
-        <v>787</v>
+        <v>805</v>
       </c>
       <c r="E333" s="15" t="s">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="F333" s="16" t="n">
         <v>40088</v>
@@ -25562,13 +25682,13 @@
         <v>72</v>
       </c>
       <c r="C334" s="15" t="s">
-        <v>793</v>
+        <v>811</v>
       </c>
       <c r="D334" s="15" t="s">
-        <v>794</v>
+        <v>812</v>
       </c>
       <c r="E334" s="15" t="s">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="F334" s="16" t="n">
         <v>45497</v>
@@ -25618,13 +25738,13 @@
         <v>72</v>
       </c>
       <c r="C335" s="15" t="s">
-        <v>795</v>
+        <v>813</v>
       </c>
       <c r="D335" s="15" t="s">
-        <v>794</v>
+        <v>812</v>
       </c>
       <c r="E335" s="15" t="s">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="F335" s="16" t="n">
         <v>46057</v>
@@ -25674,13 +25794,13 @@
         <v>72</v>
       </c>
       <c r="C336" s="15" t="s">
-        <v>796</v>
+        <v>814</v>
       </c>
       <c r="D336" s="15" t="s">
-        <v>794</v>
+        <v>812</v>
       </c>
       <c r="E336" s="15" t="s">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="F336" s="16" t="n">
         <v>42156</v>
@@ -25730,13 +25850,13 @@
         <v>72</v>
       </c>
       <c r="C337" s="15" t="s">
-        <v>797</v>
+        <v>815</v>
       </c>
       <c r="D337" s="15" t="s">
-        <v>794</v>
+        <v>812</v>
       </c>
       <c r="E337" s="15" t="s">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="F337" s="16" t="n">
         <v>45819</v>
@@ -25786,13 +25906,13 @@
         <v>72</v>
       </c>
       <c r="C338" s="15" t="s">
-        <v>798</v>
+        <v>816</v>
       </c>
       <c r="D338" s="15" t="s">
-        <v>794</v>
+        <v>812</v>
       </c>
       <c r="E338" s="15" t="s">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="F338" s="16" t="n">
         <v>45968</v>
@@ -25844,13 +25964,13 @@
         <v>72</v>
       </c>
       <c r="C339" s="15" t="s">
-        <v>799</v>
+        <v>817</v>
       </c>
       <c r="D339" s="15" t="s">
-        <v>794</v>
+        <v>812</v>
       </c>
       <c r="E339" s="15" t="s">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="F339" s="16" t="n">
         <v>46077</v>
@@ -25900,13 +26020,13 @@
         <v>72</v>
       </c>
       <c r="C340" s="15" t="s">
-        <v>800</v>
+        <v>818</v>
       </c>
       <c r="D340" s="15" t="s">
-        <v>794</v>
+        <v>812</v>
       </c>
       <c r="E340" s="15" t="s">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="F340" s="16" t="n">
         <v>42380</v>
@@ -25956,13 +26076,13 @@
         <v>72</v>
       </c>
       <c r="C341" s="15" t="s">
-        <v>801</v>
+        <v>819</v>
       </c>
       <c r="D341" s="15" t="s">
-        <v>802</v>
+        <v>820</v>
       </c>
       <c r="E341" s="15" t="s">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="F341" s="16" t="n">
         <v>45859</v>
@@ -26012,13 +26132,13 @@
         <v>72</v>
       </c>
       <c r="C342" s="15" t="s">
-        <v>803</v>
+        <v>821</v>
       </c>
       <c r="D342" s="15" t="s">
-        <v>802</v>
+        <v>820</v>
       </c>
       <c r="E342" s="15" t="s">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="F342" s="16" t="n">
         <v>45034</v>
@@ -26068,13 +26188,13 @@
         <v>72</v>
       </c>
       <c r="C343" s="15" t="s">
-        <v>804</v>
+        <v>822</v>
       </c>
       <c r="D343" s="15" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="E343" s="15" t="s">
-        <v>805</v>
+        <v>823</v>
       </c>
       <c r="F343" s="16" t="n">
         <v>46223</v>
@@ -26126,13 +26246,13 @@
         <v>72</v>
       </c>
       <c r="C344" s="15" t="s">
-        <v>806</v>
+        <v>824</v>
       </c>
       <c r="D344" s="15" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="E344" s="15" t="s">
-        <v>805</v>
+        <v>823</v>
       </c>
       <c r="F344" s="16" t="n">
         <v>46155</v>
@@ -26182,13 +26302,13 @@
         <v>72</v>
       </c>
       <c r="C345" s="15" t="s">
-        <v>807</v>
+        <v>825</v>
       </c>
       <c r="D345" s="15" t="s">
         <v>95</v>
       </c>
       <c r="E345" s="15" t="s">
-        <v>805</v>
+        <v>823</v>
       </c>
       <c r="F345" s="16" t="n">
         <v>46156</v>
@@ -26238,13 +26358,13 @@
         <v>72</v>
       </c>
       <c r="C346" s="15" t="s">
-        <v>808</v>
+        <v>826</v>
       </c>
       <c r="D346" s="15" t="s">
         <v>95</v>
       </c>
       <c r="E346" s="15" t="s">
-        <v>805</v>
+        <v>823</v>
       </c>
       <c r="F346" s="16" t="n">
         <v>45793</v>
@@ -26294,13 +26414,13 @@
         <v>72</v>
       </c>
       <c r="C347" s="15" t="s">
-        <v>809</v>
+        <v>827</v>
       </c>
       <c r="D347" s="15" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="E347" s="15" t="s">
-        <v>805</v>
+        <v>823</v>
       </c>
       <c r="F347" s="16" t="n">
         <v>40931</v>
@@ -26350,10 +26470,10 @@
         <v>72</v>
       </c>
       <c r="C348" s="15" t="s">
-        <v>810</v>
+        <v>828</v>
       </c>
       <c r="D348" s="15" t="s">
-        <v>665</v>
+        <v>683</v>
       </c>
       <c r="E348" s="15" t="s">
         <v>76</v>
@@ -26406,7 +26526,7 @@
         <v>72</v>
       </c>
       <c r="C349" s="15" t="s">
-        <v>811</v>
+        <v>829</v>
       </c>
       <c r="D349" s="15" t="s">
         <v>75</v>
@@ -26462,7 +26582,7 @@
         <v>72</v>
       </c>
       <c r="C350" s="15" t="s">
-        <v>812</v>
+        <v>830</v>
       </c>
       <c r="D350" s="15" t="s">
         <v>75</v>
@@ -26520,10 +26640,10 @@
         <v>72</v>
       </c>
       <c r="C351" s="15" t="s">
-        <v>813</v>
+        <v>831</v>
       </c>
       <c r="D351" s="15" t="s">
-        <v>676</v>
+        <v>694</v>
       </c>
       <c r="E351" s="15" t="s">
         <v>76</v>
@@ -26578,10 +26698,10 @@
         <v>72</v>
       </c>
       <c r="C352" s="15" t="s">
-        <v>814</v>
+        <v>832</v>
       </c>
       <c r="D352" s="15" t="s">
-        <v>676</v>
+        <v>694</v>
       </c>
       <c r="E352" s="15" t="s">
         <v>76</v>
@@ -26636,10 +26756,10 @@
         <v>72</v>
       </c>
       <c r="C353" s="15" t="s">
-        <v>815</v>
+        <v>833</v>
       </c>
       <c r="D353" s="15" t="s">
-        <v>676</v>
+        <v>694</v>
       </c>
       <c r="E353" s="15" t="s">
         <v>76</v>
@@ -26692,13 +26812,13 @@
         <v>72</v>
       </c>
       <c r="C354" s="15" t="s">
-        <v>816</v>
+        <v>834</v>
       </c>
       <c r="D354" s="15" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="E354" s="15" t="s">
-        <v>817</v>
+        <v>835</v>
       </c>
       <c r="F354" s="16" t="n">
         <v>46162</v>
@@ -26750,13 +26870,13 @@
         <v>72</v>
       </c>
       <c r="C355" s="15" t="s">
-        <v>818</v>
+        <v>836</v>
       </c>
       <c r="D355" s="15" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="E355" s="15" t="s">
-        <v>817</v>
+        <v>835</v>
       </c>
       <c r="F355" s="16" t="n">
         <v>44713</v>
@@ -26806,13 +26926,13 @@
         <v>72</v>
       </c>
       <c r="C356" s="15" t="s">
-        <v>819</v>
+        <v>837</v>
       </c>
       <c r="D356" s="15" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="E356" s="15" t="s">
-        <v>817</v>
+        <v>835</v>
       </c>
       <c r="F356" s="16" t="n">
         <v>46162</v>
@@ -26864,13 +26984,13 @@
         <v>81</v>
       </c>
       <c r="C357" s="15" t="s">
-        <v>820</v>
+        <v>838</v>
       </c>
       <c r="D357" s="15" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="E357" s="15" t="s">
-        <v>821</v>
+        <v>839</v>
       </c>
       <c r="F357" s="16" t="n">
         <v>46245</v>
@@ -26920,7 +27040,7 @@
         <v>81</v>
       </c>
       <c r="C358" s="15" t="s">
-        <v>822</v>
+        <v>840</v>
       </c>
       <c r="D358" s="15" t="s">
         <v>75</v>
@@ -26976,13 +27096,13 @@
         <v>81</v>
       </c>
       <c r="C359" s="15" t="s">
-        <v>823</v>
+        <v>841</v>
       </c>
       <c r="D359" s="15" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="E359" s="15" t="s">
-        <v>824</v>
+        <v>842</v>
       </c>
       <c r="F359" s="16" t="n">
         <v>41351</v>
@@ -27032,13 +27152,13 @@
         <v>81</v>
       </c>
       <c r="C360" s="15" t="s">
-        <v>825</v>
+        <v>843</v>
       </c>
       <c r="D360" s="15" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="E360" s="15" t="s">
-        <v>824</v>
+        <v>842</v>
       </c>
       <c r="F360" s="16" t="n">
         <v>45852</v>
@@ -27587,7 +27707,7 @@
       </c>
       <c r="N369" s="12" t="str">
         <f aca="false">IFERROR(INDEX('Перечень должностей'!$F$2:$F$46,MATCH(H369,'Перечень должностей'!$A$2:$A$46,0)),"")</f>
-        <v>Да</v>
+        <v>Проверить</v>
       </c>
       <c r="O369" s="17"/>
       <c r="P369" s="16" t="str">
@@ -27779,42 +27899,42 @@
   </sheetData>
   <autoFilter ref="A1:R372"/>
   <conditionalFormatting sqref="K2:K372">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>K2=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M372">
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>AND(M2&lt;&gt;"",M2&lt;TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>AND(M2&lt;&gt;"",M2&gt;=TODAY(),M2-TODAY()&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>AND(M2&lt;&gt;"",M2-TODAY()&gt;30)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N372">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
       <formula>EXACT(N2,"Да")</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
       <formula>EXACT(N2,"Проверить")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P372">
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>AND(P2&lt;&gt;"",P2&lt;TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>AND(P2&lt;&gt;"",P2&gt;=TODAY(),P2-TODAY()&lt;=30)</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>AND(P2&lt;&gt;"",P2-TODAY()&gt;30)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q372">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>Q2="ДА"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -27849,12 +27969,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>826</v>
+        <v>844</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>827</v>
+        <v>845</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27862,12 +27982,12 @@
         <v>31</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>828</v>
+        <v>846</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>829</v>
+        <v>847</v>
       </c>
       <c r="B5" s="21" t="n">
         <f aca="false">COUNTA('Учёт медосмотров'!$C$2:$C$372)</f>
@@ -27876,7 +27996,7 @@
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>830</v>
+        <v>848</v>
       </c>
       <c r="B6" s="21" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$K$2:$K$372,"&lt;&gt;")</f>
@@ -27885,7 +28005,7 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>831</v>
+        <v>849</v>
       </c>
       <c r="B7" s="21" t="n">
         <f aca="false">COUNTBLANK('Учёт медосмотров'!$K$2:$K$372)</f>
@@ -27894,7 +28014,7 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>832</v>
+        <v>850</v>
       </c>
       <c r="B8" s="21" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$L$2:$L$372,"&lt;&gt;")</f>
@@ -27903,7 +28023,7 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>833</v>
+        <v>851</v>
       </c>
       <c r="B9" s="21" t="n">
         <f aca="true">COUNTIFS('Учёт медосмотров'!$M$2:$M$372,"&lt;&gt;",'Учёт медосмотров'!$M$2:$M$372,"&lt;"&amp;TODAY())</f>
@@ -27912,7 +28032,7 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>834</v>
+        <v>852</v>
       </c>
       <c r="B10" s="21" t="n">
         <f aca="true">COUNTIFS('Учёт медосмотров'!$M$2:$M$372,"&lt;&gt;",'Учёт медосмотров'!$M$2:$M$372,"&gt;="&amp;TODAY(),'Учёт медосмотров'!$M$2:$M$372,"&lt;="&amp;(TODAY()+30))</f>
@@ -27921,7 +28041,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>835</v>
+        <v>853</v>
       </c>
       <c r="B11" s="21" t="n">
         <f aca="true">COUNTIFS('Учёт медосмотров'!$F$2:$F$372,"&lt;"&amp;(TODAY()-365),'Учёт медосмотров'!$K$2:$K$372,"")</f>
@@ -27930,7 +28050,7 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>836</v>
+        <v>854</v>
       </c>
       <c r="B12" s="21" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$Q$2:$Q$372,"ДА")</f>
@@ -27939,25 +28059,25 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>837</v>
+        <v>855</v>
       </c>
       <c r="B13" s="21" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$N$2:$N$372,"Да")</f>
-        <v>50</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>838</v>
+        <v>856</v>
       </c>
       <c r="B14" s="21" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$N$2:$N$372,"Проверить")</f>
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>839</v>
+        <v>857</v>
       </c>
       <c r="B15" s="21" t="n">
         <f aca="false">COUNTIFS('Учёт медосмотров'!$N$2:$N$372,"Да",'Учёт медосмотров'!$O$2:$O$372,"&lt;&gt;")</f>
@@ -27966,7 +28086,7 @@
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>840</v>
+        <v>858</v>
       </c>
       <c r="B16" s="21" t="n">
         <f aca="true">COUNTIFS('Учёт медосмотров'!$P$2:$P$372,"&lt;&gt;",'Учёт медосмотров'!$P$2:$P$372,"&lt;"&amp;TODAY())</f>
@@ -27975,7 +28095,7 @@
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>841</v>
+        <v>859</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27983,15 +28103,15 @@
         <v>44</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>842</v>
+        <v>860</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>843</v>
+        <v>861</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="B20" s="12" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$B$2:$B$372,A20)</f>
@@ -28017,7 +28137,7 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>737</v>
+        <v>755</v>
       </c>
       <c r="B22" s="12" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$B$2:$B$372,A22)</f>
@@ -28030,7 +28150,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="B23" s="12" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$B$2:$B$372,A23)</f>
@@ -28056,7 +28176,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="B25" s="12" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$B$2:$B$372,A25)</f>
@@ -28082,7 +28202,7 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="B27" s="12" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$B$2:$B$372,A27)</f>
@@ -28118,18 +28238,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>844</v>
+        <v>862</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>845</v>
+        <v>863</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>846</v>
+        <v>864</v>
       </c>
       <c r="B2" s="22" t="n">
         <v>18</v>
@@ -28137,7 +28257,7 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>847</v>
+        <v>865</v>
       </c>
       <c r="B3" s="22" t="n">
         <v>19</v>
@@ -28145,7 +28265,7 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>848</v>
+        <v>866</v>
       </c>
       <c r="B4" s="22" t="n">
         <v>28</v>
@@ -28153,7 +28273,7 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>849</v>
+        <v>867</v>
       </c>
       <c r="B5" s="22" t="n">
         <v>28</v>
@@ -28161,7 +28281,7 @@
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>850</v>
+        <v>868</v>
       </c>
       <c r="B6" s="22" t="n">
         <v>27</v>
@@ -28169,7 +28289,7 @@
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>851</v>
+        <v>869</v>
       </c>
       <c r="B7" s="22" t="n">
         <v>9</v>
@@ -28177,7 +28297,7 @@
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>852</v>
+        <v>870</v>
       </c>
       <c r="B8" s="22" t="n">
         <v>27</v>
@@ -28185,7 +28305,7 @@
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>853</v>
+        <v>871</v>
       </c>
       <c r="B9" s="22" t="n">
         <v>27</v>
@@ -28193,7 +28313,7 @@
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>854</v>
+        <v>872</v>
       </c>
       <c r="B10" s="22" t="n">
         <v>39</v>
@@ -28201,7 +28321,7 @@
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>855</v>
+        <v>873</v>
       </c>
       <c r="B11" s="22" t="n">
         <v>39</v>
@@ -28209,7 +28329,7 @@
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>856</v>
+        <v>874</v>
       </c>
       <c r="B12" s="22" t="n">
         <v>38</v>
@@ -28217,7 +28337,7 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>857</v>
+        <v>875</v>
       </c>
       <c r="B13" s="22" t="n">
         <v>6</v>
@@ -28225,7 +28345,7 @@
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>858</v>
+        <v>876</v>
       </c>
       <c r="B14" s="22" t="n">
         <v>5</v>
@@ -28233,7 +28353,7 @@
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>859</v>
+        <v>877</v>
       </c>
       <c r="B15" s="22" t="n">
         <v>28</v>
@@ -28241,7 +28361,7 @@
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>860</v>
+        <v>878</v>
       </c>
       <c r="B16" s="22" t="n">
         <v>28</v>
@@ -28249,7 +28369,7 @@
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>861</v>
+        <v>879</v>
       </c>
       <c r="B17" s="22" t="n">
         <v>42</v>
@@ -28257,7 +28377,7 @@
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>862</v>
+        <v>880</v>
       </c>
       <c r="B18" s="22" t="n">
         <v>42</v>
@@ -28265,7 +28385,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>863</v>
+        <v>881</v>
       </c>
       <c r="B19" s="22" t="n">
         <v>13</v>
@@ -28273,7 +28393,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>864</v>
+        <v>882</v>
       </c>
       <c r="B20" s="22" t="n">
         <v>27</v>
@@ -28281,7 +28401,7 @@
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>865</v>
+        <v>883</v>
       </c>
       <c r="B21" s="22" t="n">
         <v>40</v>
@@ -28289,7 +28409,7 @@
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>866</v>
+        <v>884</v>
       </c>
       <c r="B22" s="22" t="n">
         <v>17</v>
@@ -28297,7 +28417,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>867</v>
+        <v>885</v>
       </c>
       <c r="B23" s="22" t="n">
         <v>4</v>
@@ -28305,7 +28425,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>868</v>
+        <v>886</v>
       </c>
       <c r="B24" s="22" t="n">
         <v>11</v>
@@ -28313,7 +28433,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>869</v>
+        <v>887</v>
       </c>
       <c r="B25" s="22" t="n">
         <v>2</v>
@@ -28321,7 +28441,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>870</v>
+        <v>888</v>
       </c>
       <c r="B26" s="22" t="n">
         <v>14</v>
@@ -28329,7 +28449,7 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>871</v>
+        <v>889</v>
       </c>
       <c r="B27" s="22" t="n">
         <v>14</v>
@@ -28337,7 +28457,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>872</v>
+        <v>890</v>
       </c>
       <c r="B28" s="22" t="n">
         <v>13</v>
@@ -28345,7 +28465,7 @@
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>873</v>
+        <v>891</v>
       </c>
       <c r="B29" s="22" t="n">
         <v>15</v>
@@ -28353,7 +28473,7 @@
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>874</v>
+        <v>892</v>
       </c>
       <c r="B30" s="22" t="n">
         <v>36</v>
@@ -28361,7 +28481,7 @@
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>875</v>
+        <v>893</v>
       </c>
       <c r="B31" s="22" t="n">
         <v>18</v>
@@ -28369,7 +28489,7 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>876</v>
+        <v>894</v>
       </c>
       <c r="B32" s="22" t="n">
         <v>18</v>
@@ -28377,7 +28497,7 @@
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>877</v>
+        <v>895</v>
       </c>
       <c r="B33" s="22" t="n">
         <v>29</v>
@@ -28385,7 +28505,7 @@
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>878</v>
+        <v>896</v>
       </c>
       <c r="B34" s="22" t="n">
         <v>29</v>
@@ -28393,7 +28513,7 @@
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>879</v>
+        <v>897</v>
       </c>
       <c r="B35" s="22" t="n">
         <v>22</v>
@@ -28401,7 +28521,7 @@
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>880</v>
+        <v>898</v>
       </c>
       <c r="B36" s="22" t="n">
         <v>3</v>
@@ -28409,7 +28529,7 @@
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>881</v>
+        <v>899</v>
       </c>
       <c r="B37" s="22" t="n">
         <v>11</v>
@@ -28417,7 +28537,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>882</v>
+        <v>900</v>
       </c>
       <c r="B38" s="22" t="n">
         <v>37</v>
@@ -28425,7 +28545,7 @@
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>883</v>
+        <v>901</v>
       </c>
       <c r="B39" s="22" t="n">
         <v>23</v>
@@ -28433,7 +28553,7 @@
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>884</v>
+        <v>902</v>
       </c>
       <c r="B40" s="22" t="n">
         <v>45</v>
@@ -28441,7 +28561,7 @@
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="B41" s="22" t="n">
         <v>31</v>
@@ -28449,7 +28569,7 @@
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>886</v>
+        <v>904</v>
       </c>
       <c r="B42" s="22" t="n">
         <v>35</v>
@@ -28457,7 +28577,7 @@
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>887</v>
+        <v>905</v>
       </c>
       <c r="B43" s="22" t="n">
         <v>16</v>
@@ -28465,7 +28585,7 @@
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>888</v>
+        <v>906</v>
       </c>
       <c r="B44" s="22" t="n">
         <v>30</v>
@@ -28473,7 +28593,7 @@
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>889</v>
+        <v>907</v>
       </c>
       <c r="B45" s="22" t="n">
         <v>43</v>
@@ -28481,7 +28601,7 @@
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>890</v>
+        <v>908</v>
       </c>
       <c r="B46" s="22" t="n">
         <v>25</v>
@@ -28489,7 +28609,7 @@
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>891</v>
+        <v>909</v>
       </c>
       <c r="B47" s="22" t="n">
         <v>1</v>
@@ -28497,7 +28617,7 @@
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>892</v>
+        <v>910</v>
       </c>
       <c r="B48" s="22" t="n">
         <v>7</v>
@@ -28505,7 +28625,7 @@
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>893</v>
+        <v>911</v>
       </c>
       <c r="B49" s="22" t="n">
         <v>9</v>
@@ -28513,7 +28633,7 @@
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>894</v>
+        <v>912</v>
       </c>
       <c r="B50" s="22" t="n">
         <v>26</v>
@@ -28521,7 +28641,7 @@
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>895</v>
+        <v>913</v>
       </c>
       <c r="B51" s="22" t="n">
         <v>32</v>
@@ -28529,7 +28649,7 @@
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>896</v>
+        <v>914</v>
       </c>
       <c r="B52" s="22" t="n">
         <v>41</v>
@@ -28537,7 +28657,7 @@
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>897</v>
+        <v>915</v>
       </c>
       <c r="B53" s="22" t="n">
         <v>8</v>
@@ -28545,7 +28665,7 @@
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>898</v>
+        <v>916</v>
       </c>
       <c r="B54" s="22" t="n">
         <v>19</v>
@@ -28553,7 +28673,7 @@
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>899</v>
+        <v>917</v>
       </c>
       <c r="B55" s="22" t="n">
         <v>19</v>
@@ -28561,7 +28681,7 @@
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>900</v>
+        <v>918</v>
       </c>
       <c r="B56" s="22" t="n">
         <v>12</v>
@@ -28569,7 +28689,7 @@
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>901</v>
+        <v>919</v>
       </c>
       <c r="B57" s="22" t="n">
         <v>44</v>
@@ -28577,7 +28697,7 @@
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>902</v>
+        <v>920</v>
       </c>
       <c r="B58" s="22" t="n">
         <v>14</v>
@@ -28585,7 +28705,7 @@
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>903</v>
+        <v>921</v>
       </c>
       <c r="B59" s="22" t="n">
         <v>45</v>
@@ -28593,7 +28713,7 @@
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
-        <v>904</v>
+        <v>922</v>
       </c>
       <c r="B60" s="22" t="n">
         <v>45</v>
@@ -28601,7 +28721,7 @@
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>905</v>
+        <v>923</v>
       </c>
       <c r="B61" s="22" t="n">
         <v>44</v>
@@ -28609,7 +28729,7 @@
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>906</v>
+        <v>924</v>
       </c>
       <c r="B62" s="22" t="n">
         <v>45</v>
@@ -28617,7 +28737,7 @@
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>907</v>
+        <v>925</v>
       </c>
       <c r="B63" s="22" t="n">
         <v>10</v>
@@ -28625,7 +28745,7 @@
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="B64" s="22" t="n">
         <v>21</v>
@@ -28633,7 +28753,7 @@
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="B65" s="22" t="n">
         <v>24</v>
@@ -28641,7 +28761,7 @@
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
-        <v>910</v>
+        <v>928</v>
       </c>
       <c r="B66" s="22" t="n">
         <v>45</v>
@@ -28649,7 +28769,7 @@
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
-        <v>911</v>
+        <v>929</v>
       </c>
       <c r="B67" s="22" t="n">
         <v>10</v>
@@ -28657,7 +28777,7 @@
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
-        <v>912</v>
+        <v>930</v>
       </c>
       <c r="B68" s="22" t="n">
         <v>34</v>
@@ -28665,7 +28785,7 @@
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
-        <v>913</v>
+        <v>931</v>
       </c>
       <c r="B69" s="22" t="n">
         <v>10</v>
@@ -28673,7 +28793,7 @@
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
-        <v>914</v>
+        <v>932</v>
       </c>
       <c r="B70" s="22" t="n">
         <v>10</v>
@@ -28681,7 +28801,7 @@
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
-        <v>915</v>
+        <v>933</v>
       </c>
       <c r="B71" s="22" t="n">
         <v>33</v>
@@ -28689,7 +28809,7 @@
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
-        <v>916</v>
+        <v>934</v>
       </c>
       <c r="B72" s="22" t="n">
         <v>20</v>
@@ -28697,7 +28817,7 @@
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
-        <v>917</v>
+        <v>935</v>
       </c>
       <c r="B73" s="22" t="n">
         <v>2</v>
@@ -28705,35 +28825,35 @@
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="s">
-        <v>918</v>
+        <v>936</v>
       </c>
       <c r="B74" s="22" t="n">
         <v>30</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>919</v>
+        <v>937</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="s">
-        <v>920</v>
+        <v>938</v>
       </c>
       <c r="B75" s="22" t="n">
         <v>21</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>921</v>
+        <v>939</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
-        <v>922</v>
+        <v>940</v>
       </c>
       <c r="B76" s="22" t="n">
         <v>36</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>921</v>
+        <v>939</v>
       </c>
     </row>
   </sheetData>
@@ -28766,17 +28886,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>923</v>
+        <v>941</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>924</v>
+        <v>942</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>925</v>
+        <v>943</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>44</v>
@@ -28794,7 +28914,7 @@
         <v>45</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Медосмотры_сверка_штатка_05.10.2026.xlsx
+++ b/Медосмотры_сверка_штатка_05.10.2026.xlsx
@@ -100,7 +100,7 @@
     <t xml:space="preserve">5. Ни для одного сотрудника ещё не зафиксирована дата фактически пройденного периодического осмотра, поэтому все расчётные даты очередного осмотра - это первый плановый цикл от даты предварительного осмотра. По мере прохождения периодических осмотров вносите их даты в столбец «Факт. дата последнего пройденного периодического осмотра», и следующая дата пересчитается автоматически.</t>
   </si>
   <si>
-    <t xml:space="preserve">6. Список должностей, подлежащих психиатрическому освидетельствованию по Приказу №342н, определён по названию должности и общей логике вида деятельности (управление транспортом - п.1 Приложения №2; работа с электроустановками - п.11-12), это помечено «Да». Для должностей Главный механик, Сборщик стеклопластиковых изделий, Старший сторож/сторож/старший оперативный дежурный/оперативный дежурный совпадение с категориями Приложения №2 первоначально выглядело вероятным (сосуды под давлением/автоклавы, оружие у охраны), но специалист по охране труда подтвердил, что эти должности освидетельствование не проходят, - в столбце «Психиатрическое освидетельствование» проставлено «Нет» с примечанием об этом уточнении. ИСПРАВЛЕНО 13.10.2026: по Приказу №342н (с 01.09.2022) периодичность освидетельствования не установлена (письмо Минздрава №30-0/3066769); дата «+5 лет» в столбце P — только внутренняя контрольная мера, не требование закона («5 лет» в ст.6 Закона №3185-1 — срок временной непригодности, а не периодичность). С 01.03.2026 действуют изменения 342н (Приказ №392н от 02.07.2025) — нумерацию пунктов Приложения №2 сверить. УТОЧНЕНО 13.10.2026 по тексту 342н: п.11 Приложения №2 относится к сфере электроэнергетики (35-ФЗ) — для электромонтажников и мастеров электромонтажных участков (п.20, п.29 Перечня) статус изменён на «Проверить».</t>
+    <t xml:space="preserve">6. Список должностей, подлежащих психиатрическому освидетельствованию по Приказу №342н, определён по названию должности и общей логике вида деятельности (управление транспортом - п.1 Приложения №2; работа с электроустановками - п.11-12), это помечено «Да». Для должностей Главный механик, Сборщик стеклопластиковых изделий, Старший сторож/сторож/старший оперативный дежурный/оперативный дежурный совпадение с категориями Приложения №2 первоначально выглядело вероятным (сосуды под давлением/автоклавы, оружие у охраны), но специалист по охране труда подтвердил, что эти должности освидетельствование не проходят, - в столбце «Психиатрическое освидетельствование» проставлено «Нет» с примечанием об этом уточнении. ИСПРАВЛЕНО 13.10.2026: по Приказу №342н (с 01.09.2022) периодичность освидетельствования не установлена (письмо Минздрава №30-0/3066769); дата «+5 лет» в столбце P — только внутренняя контрольная мера, не требование закона («5 лет» в ст.6 Закона №3185-1 — срок временной непригодности, а не периодичность). С 01.03.2026 действуют изменения 342н (Приказ №392н от 02.07.2025) — нумерацию пунктов Приложения №2 сверить. УТОЧНЕНО 13.10.2026 по тексту 342н: п.11 Приложения №2 касается работ с электроустановками «в сфере электроэнергетики»; официального разъяснения нет, применимость к монтажу бортового ЭО спорна — для п.20 и п.29 Перечня статус изменён на «Проверить» (решение работодателя с обоснованием).</t>
   </si>
   <si>
     <t xml:space="preserve">7. ИСПРАВЛЕНО 10.09.2026: список сотрудников пересобран заново напрямую из штатного расписания (736 сотрудников на 04.09.2026), а не из ранее использовавшегося отдельного файла учёта - тот файл оказался неполным и не отражал новых сотрудников (например, Раззакову Светлану Владимировну, уборщика производственных и служебных помещений, принятую 27.08.2026, - обнаружено пользователем при ручной проверке). При пересборке также учтено, что должности в штатном расписании содержат разряд/категорию (например, «Столяр 5 разряда», «Инженер 2 категории») - формула сопоставления на листе «Учёт медосмотров» (столбец G) теперь отбрасывает эти суффиксы при поиске пункта Перечня. В результате: добавлено 21 новых сотрудника (включая Раззакову С.В.), исключено 10 - из них 6 больше не значатся в штатном расписании (уволены), а 4 (Добролюбова Г.М., Кляцкин А.Б., Лазебников В.В., Пушкин С.О.) переведены на должности вне перечня Приказа №43. Итоговая численность выросла с 352 до 363 человек. Также обнаружено: по должности «Инженер по эксплуатации» (№17 Перечня) сейчас нет ни одного сотрудника в штате - это не ошибка, а фактическое отсутствие занятых ставок. Рекомендуется впредь сверять этот файл со штатным расписанием при каждом обновлении последнего, так как найденный пробел показывает, что расхождения возникают быстро.</t>
@@ -802,10 +802,10 @@
     <t xml:space="preserve">Психиатрическое освидетельствование у бывших монтажников ЭО ЛА</t>
   </si>
   <si>
-    <t xml:space="preserve">По тексту 342н п.11 Прил.№2 касается «сферы электроэнергетики» (35-ФЗ). Электромонтажники участков РЭО (32 чел., п.20) и мастера (2 чел., п.29) монтируют бортовое ЭО изделий — по буквальному прочтению это не электроэнергетика. На листе «Перечень» для №20 и №29 статус изменён с «Да» на «Проверить». Сюда относятся и Богданов, Озорнов, Романов, Шабалин (бывшие монтажники ЭО ЛА).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Решение работодателя с фиксацией основания</t>
+    <t xml:space="preserve">п.11 Прил.№2 342н — работы с электроустановками «в сфере электроэнергетики». Официального разъяснения нет; эксперты исходят из определения электроустановки (ГОСТ 12.1.009-2017), а не из статуса организации. Для электромонтажников РЭО (32 чел., п.20) и мастеров (2 чел., п.29) применимость спорна: монтаж бортового ЭО — довод «против», работы под напряжением/испытания — довод «за». Статус на листе «Перечень» — «Проверить» (ранее «Да»). Сюда же Богданов, Озорнов, Романов, Шабалин.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Решение работодателя с письменным обоснованием; консервативный вариант — «Да»</t>
   </si>
   <si>
     <t xml:space="preserve">7.14</t>
@@ -838,10 +838,10 @@
     <t xml:space="preserve">Переводы с изменением пунктов вредности (14 чел.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Бригадиры из маляров/столяров/сборщиков (4), облицовщики из маляров/сборщика (4), слесари МСР из операторов ТПА (2), электромонтажники из монтажников ЭО ЛА (4). Если фактические факторы изменились — объём следующего периодического осмотра другой.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сверить с картами СОУТ; при новых факторах — внеочередной осмотр по направлению</t>
+    <t xml:space="preserve">14 чел. после перевода получили другие пункты вредности (бригадиры из маляров/столяров/сборщиков — 4; облицовщики из маляров/сборщика — 4; слесари МСР из операторов ТПА — 2; электромонтажники из монтажников ЭО ЛА — 4). ИСПРАВЛЕНО: «внеочередной» осмотр здесь не применим — по п.19 Порядка 29н он проводится только по медицинским рекомендациям и/или после нетрудоспособности. Для переводов в 29н норм нет. Позиция Роструда (письмо от 08.05.2024 №ПГ/08357-6-1): если факторы те же и заключение действует — повторный осмотр не нужен. Если появились НОВЫЕ факторы — работник не должен допускаться без осмотра по ним (ст.214, 76 ТК РФ).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сверить факторы по СОУТ; при новых факторах — направить на осмотр по новым факторам до допуска</t>
   </si>
   <si>
     <t xml:space="preserve">7.17</t>
@@ -1072,7 +1072,7 @@
     <t xml:space="preserve">Проверить</t>
   </si>
   <si>
-    <t xml:space="preserve">ПРОВЕРИТЬ (13.10.2026, по тексту 342н в ред. 392н): п.11 Приложения №2 — «деятельность в сфере ЭЛЕКТРОЭНЕРГЕТИКИ» (ст.3 Федерального закона №35-ФЗ) — монтаж, наладка, техобслуживание, ремонт, управление режимом электроустановок. Монтаж бортового электрооборудования/жгутов изделий (участки РЭО) к электроэнергетике, по буквальному прочтению, не относится. Решение — за работодателем: при подтверждении работ в электроустановках предприятия — «Да», иначе — «Нет»; основание зафиксировать.</t>
+    <t xml:space="preserve">ПРОВЕРИТЬ (13.10.2026). п.11 Прил.№2 342н: «деятельность в сфере электроэнергетики, связанная с... монтажом, наладкой, техобслуживанием, ремонтом, управлением режимом работы ЭЛЕКТРОУСТАНОВОК»; сноска — ст.3 35-ФЗ и ГОСТ 12.1.009-2017. Официального разъяснения Минздрава нет. Распространённая экспертная позиция: критерий — работа именно с электроустановками (по ГОСТ 12.1.009-2017), а не статус организации. Монтаж бортового ЭО изделия в обесточенном состоянии — спорно; работы под напряжением (испытания, проверка цепей) — довод за «Да». Решение работодателя с письменным обоснованием; при сомнении — запрос в Минздрав или следовать консервативному варианту «Да».</t>
   </si>
   <si>
     <t xml:space="preserve">Столяр</t>

--- a/Медосмотры_сверка_штатка_05.10.2026.xlsx
+++ b/Медосмотры_сверка_штатка_05.10.2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Инструкция" sheetId="1" state="visible" r:id="rId3"/>
@@ -17,6 +17,8 @@
     <sheet name="Выбывшие" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">Выбывшие!$A$4:$G$10</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Перечень должностей'!$A$1:$H$46</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Учёт медосмотров'!$A$1:$R$372</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -3150,7 +3152,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
+          <fgColor rgb="FFFFFF00"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -3158,7 +3160,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
+          <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -3380,6 +3382,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TblUchet" displayName="TblUchet" ref="A1:Q366" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <autoFilter ref="A1:Q366"/>
@@ -6664,6 +6674,7 @@
       <c r="H49" s="14"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H46"/>
   <mergeCells count="2">
     <mergeCell ref="A48:H48"/>
     <mergeCell ref="A49:H49"/>
@@ -6675,6 +6686,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -28045,7 +28057,7 @@
       </c>
       <c r="B11" s="21" t="n">
         <f aca="true">COUNTIFS('Учёт медосмотров'!$F$2:$F$372,"&lt;"&amp;(TODAY()-365),'Учёт медосмотров'!$K$2:$K$372,"")</f>
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29052,6 +29064,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:G10"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -29059,5 +29072,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>